--- a/example data/5mm/Results/ID 15 - Run 3/ID 15 - Run 3 - Original Stepcycles.xlsx
+++ b/example data/5mm/Results/ID 15 - Run 3/ID 15 - Run 3 - Original Stepcycles.xlsx
@@ -666,67 +666,67 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
+          <t>Hind paw tao Velocity</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Acceleration</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Velocity</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Acceleration</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Velocity</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Acceleration</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Velocity</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Acceleration</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Velocity</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Acceleration</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
           <t>Ankle Angle</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Velocity</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Acceleration</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Velocity</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Acceleration</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Velocity</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Acceleration</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Velocity</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Acceleration</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Velocity</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Acceleration</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
@@ -780,7 +780,7 @@
         <v>104.9621419703707</v>
       </c>
       <c r="G2" t="n">
-        <v>13.9228009163065</v>
+        <v>13.92280091630652</v>
       </c>
       <c r="H2" t="n">
         <v>0.9996265172958374</v>
@@ -789,7 +789,7 @@
         <v>87.53980271359708</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2568508716339863</v>
+        <v>-0.2568508716339761</v>
       </c>
       <c r="K2" t="n">
         <v>0.9990825653076172</v>
@@ -798,7 +798,7 @@
         <v>84.0116541436378</v>
       </c>
       <c r="M2" t="n">
-        <v>3.003790023479041</v>
+        <v>3.003790023479056</v>
       </c>
       <c r="N2" t="n">
         <v>0.9994613528251648</v>
@@ -807,7 +807,7 @@
         <v>83.02066884142288</v>
       </c>
       <c r="P2" t="n">
-        <v>12.77423615151264</v>
+        <v>12.77423615151263</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9788652658462524</v>
@@ -816,7 +816,7 @@
         <v>92.77886735632065</v>
       </c>
       <c r="S2" t="n">
-        <v>15.49021944086601</v>
+        <v>15.49021944086602</v>
       </c>
       <c r="T2" t="n">
         <v>0.9901330471038818</v>
@@ -825,7 +825,7 @@
         <v>89.57968366906998</v>
       </c>
       <c r="V2" t="n">
-        <v>24.84183615826547</v>
+        <v>24.84183615826546</v>
       </c>
       <c r="W2" t="n">
         <v>0.9766482710838318</v>
@@ -834,7 +834,7 @@
         <v>46.64308669719291</v>
       </c>
       <c r="Y2" t="n">
-        <v>26.67065884204624</v>
+        <v>26.67065884204621</v>
       </c>
       <c r="Z2" t="n">
         <v>0.9888256192207336</v>
@@ -843,7 +843,7 @@
         <v>41.89148760856467</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.9840763173205</v>
+        <v>18.98407631732048</v>
       </c>
       <c r="AC2" t="n">
         <v>0.995270311832428</v>
@@ -852,7 +852,7 @@
         <v>45.94570728058511</v>
       </c>
       <c r="AE2" t="n">
-        <v>11.04397063559676</v>
+        <v>11.04397063559674</v>
       </c>
       <c r="AF2" t="n">
         <v>0.9742745161056519</v>
@@ -870,7 +870,7 @@
         <v>35.87370933370387</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.3790672789228609</v>
+        <v>-0.3790672789228723</v>
       </c>
       <c r="AL2" t="n">
         <v>0.9982078075408936</v>
@@ -888,7 +888,7 @@
         <v>15.91039819920317</v>
       </c>
       <c r="AQ2" t="n">
-        <v>28.51265440595913</v>
+        <v>28.51265440595911</v>
       </c>
       <c r="AR2" t="n">
         <v>0.8818411231040955</v>
@@ -897,67 +897,67 @@
         <v>7.437257056540632</v>
       </c>
       <c r="AT2" t="n">
-        <v>18.55783665433844</v>
+        <v>18.55783665433843</v>
       </c>
       <c r="AU2" t="n">
         <v>0.2042872309684753</v>
       </c>
       <c r="AV2" t="n">
-        <v>85.72928785616436</v>
+        <v>8.52018315741357</v>
       </c>
       <c r="AW2" t="n">
-        <v>65.93804011739417</v>
+        <v>0.2185983860746319</v>
       </c>
       <c r="AX2" t="n">
+        <v>4.204729770092257</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.045178352518281</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3.774411627586851</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-0.06986171641248262</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.688750246737861</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.00288537208070494</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.584450742031663</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-0.240155483813993</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>85.72928785616429</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>65.93804011739408</v>
+      </c>
+      <c r="BH2" t="n">
         <v>121.2281049574258</v>
       </c>
-      <c r="AY2" t="n">
-        <v>8.52018315741357</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.2185983860746319</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.204729770092257</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.045178352518281</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.774411627586851</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-0.06986171641248262</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.688750246737861</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.00288537208070494</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.584450742031663</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>-0.240155483813993</v>
-      </c>
       <c r="BI2" t="n">
-        <v>-3.021471494610367</v>
+        <v>-3.021471494610267</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.1678550591524584</v>
+        <v>0.1678550591524086</v>
       </c>
       <c r="BK2" t="n">
         <v>0.7187257839893846</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.373736436052425</v>
+        <v>1.373736436052475</v>
       </c>
       <c r="BM2" t="n">
-        <v>-17.53727741735243</v>
+        <v>-17.5372774173524</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.945257828960159</v>
+        <v>2.945257828960102</v>
       </c>
     </row>
     <row r="3">
@@ -971,7 +971,7 @@
         <v>122.971814744016</v>
       </c>
       <c r="D3" t="n">
-        <v>3.07225978120843</v>
+        <v>3.072259781208444</v>
       </c>
       <c r="E3" t="n">
         <v>0.9996121525764465</v>
@@ -980,7 +980,7 @@
         <v>105.7698432435381</v>
       </c>
       <c r="G3" t="n">
-        <v>13.01504906187665</v>
+        <v>13.01504906187666</v>
       </c>
       <c r="H3" t="n">
         <v>0.9990083575248718</v>
@@ -989,7 +989,7 @@
         <v>87.57963789270279</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1206905283826529</v>
+        <v>-0.1206905283826463</v>
       </c>
       <c r="K3" t="n">
         <v>0.9990074038505554</v>
@@ -998,7 +998,7 @@
         <v>84.06124520809092</v>
       </c>
       <c r="M3" t="n">
-        <v>3.009341625457097</v>
+        <v>3.009341625457115</v>
       </c>
       <c r="N3" t="n">
         <v>0.9994877576828003</v>
@@ -1007,7 +1007,7 @@
         <v>83.75304201815992</v>
       </c>
       <c r="P3" t="n">
-        <v>12.65557471742019</v>
+        <v>12.65557471742021</v>
       </c>
       <c r="Q3" t="n">
         <v>0.9512596130371094</v>
@@ -1016,7 +1016,7 @@
         <v>93.12299363156583</v>
       </c>
       <c r="S3" t="n">
-        <v>15.23512170669881</v>
+        <v>15.2351217066988</v>
       </c>
       <c r="T3" t="n">
         <v>0.9881139397621155</v>
@@ -1034,7 +1034,7 @@
         <v>48.22753743922457</v>
       </c>
       <c r="Y3" t="n">
-        <v>27.48857051768201</v>
+        <v>27.48857051768202</v>
       </c>
       <c r="Z3" t="n">
         <v>0.9941092729568481</v>
@@ -1043,7 +1043,7 @@
         <v>43.58023785530253</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.44956678025267</v>
+        <v>19.44956678025266</v>
       </c>
       <c r="AC3" t="n">
         <v>0.9967002272605896</v>
@@ -1052,7 +1052,7 @@
         <v>49.72011890817196</v>
       </c>
       <c r="AE3" t="n">
-        <v>13.577497766373</v>
+        <v>13.57749776637301</v>
       </c>
       <c r="AF3" t="n">
         <v>0.9807089567184448</v>
@@ -1061,7 +1061,7 @@
         <v>38.69979127924493</v>
       </c>
       <c r="AH3" t="n">
-        <v>8.91462285467918</v>
+        <v>8.914622854679189</v>
       </c>
       <c r="AI3" t="n">
         <v>0.9979701638221741</v>
@@ -1070,7 +1070,7 @@
         <v>44.39389249111744</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8585503760804443</v>
+        <v>-0.8585503760804521</v>
       </c>
       <c r="AL3" t="n">
         <v>0.9981978535652161</v>
@@ -1079,7 +1079,7 @@
         <v>32.06914130677568</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.27426342253989</v>
+        <v>23.2742634225399</v>
       </c>
       <c r="AO3" t="n">
         <v>0.999285876750946</v>
@@ -1088,7 +1088,7 @@
         <v>17.53078420111474</v>
       </c>
       <c r="AQ3" t="n">
-        <v>28.99394745522358</v>
+        <v>28.99394745522357</v>
       </c>
       <c r="AR3" t="n">
         <v>0.9059634208679199</v>
@@ -1103,61 +1103,61 @@
         <v>0.5257046222686768</v>
       </c>
       <c r="AV3" t="n">
-        <v>82.70781636155399</v>
+        <v>8.738781543488201</v>
       </c>
       <c r="AW3" t="n">
-        <v>66.65676590138355</v>
+        <v>0.3387552626589478</v>
       </c>
       <c r="AX3" t="n">
+        <v>5.249908122610538</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.290876307386032</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.704549911174368</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-0.1477383552713594</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.691635618818566</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.1955691804277162</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.34429525821767</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.06531045791950696</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>82.70781636155402</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>66.65676590138347</v>
+      </c>
+      <c r="BH3" t="n">
         <v>103.6908275400734</v>
       </c>
-      <c r="AY3" t="n">
-        <v>8.738781543488201</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.3387552626589478</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.249908122610538</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.290876307386032</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.704549911174368</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-0.1477383552713594</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.691635618818566</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0.1955691804277162</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.34429525821767</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0.06531045791950696</v>
-      </c>
       <c r="BI3" t="n">
-        <v>-2.853616435457909</v>
+        <v>-2.853616435457859</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.882320884722809</v>
+        <v>1.882320884722734</v>
       </c>
       <c r="BK3" t="n">
-        <v>2.09246222004181</v>
+        <v>2.09246222004186</v>
       </c>
       <c r="BL3" t="n">
-        <v>5.500917972930846</v>
+        <v>5.500917972930871</v>
       </c>
       <c r="BM3" t="n">
-        <v>-14.59201958839227</v>
+        <v>-14.5920195883923</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.98472877594018</v>
+        <v>4.984728775940173</v>
       </c>
     </row>
     <row r="4">
@@ -1171,7 +1171,7 @@
         <v>123.5671997070312</v>
       </c>
       <c r="D4" t="n">
-        <v>2.690627727102736</v>
+        <v>2.690627727102726</v>
       </c>
       <c r="E4" t="n">
         <v>0.9998694658279419</v>
@@ -1180,7 +1180,7 @@
         <v>106.4710332992229</v>
       </c>
       <c r="G4" t="n">
-        <v>12.74915654608543</v>
+        <v>12.74915654608544</v>
       </c>
       <c r="H4" t="n">
         <v>0.9993744492530823</v>
@@ -1189,7 +1189,7 @@
         <v>87.59696635794133</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4069064525847637</v>
+        <v>-0.406906452584774</v>
       </c>
       <c r="K4" t="n">
         <v>0.9990202188491821</v>
@@ -1198,7 +1198,7 @@
         <v>84.50612818941157</v>
       </c>
       <c r="M4" t="n">
-        <v>2.79954950860207</v>
+        <v>2.799549508602061</v>
       </c>
       <c r="N4" t="n">
         <v>0.9994401335716248</v>
@@ -1207,7 +1207,7 @@
         <v>83.94217795514047</v>
       </c>
       <c r="P4" t="n">
-        <v>12.32806266622339</v>
+        <v>12.3280626662234</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9453575015068054</v>
@@ -1225,7 +1225,7 @@
         <v>91.3061020222116</v>
       </c>
       <c r="V4" t="n">
-        <v>24.04103380568483</v>
+        <v>24.04103380568484</v>
       </c>
       <c r="W4" t="n">
         <v>0.9751635193824768</v>
@@ -1234,7 +1234,7 @@
         <v>49.33167721362825</v>
       </c>
       <c r="Y4" t="n">
-        <v>27.5656192860705</v>
+        <v>27.56561928607048</v>
       </c>
       <c r="Z4" t="n">
         <v>0.9949707388877869</v>
@@ -1261,7 +1261,7 @@
         <v>44.99487775437375</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.262014835438833</v>
+        <v>7.26201483543883</v>
       </c>
       <c r="AI4" t="n">
         <v>0.9986932873725891</v>
@@ -1270,7 +1270,7 @@
         <v>53.35127242068027</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8146245428856389</v>
+        <v>0.8146245428856383</v>
       </c>
       <c r="AL4" t="n">
         <v>0.9968138337135315</v>
@@ -1288,7 +1288,7 @@
         <v>20.55798388542013</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28.74212873742937</v>
+        <v>28.74212873742936</v>
       </c>
       <c r="AR4" t="n">
         <v>0.9292354583740234</v>
@@ -1297,67 +1297,67 @@
         <v>9.925590677464262</v>
       </c>
       <c r="AT4" t="n">
-        <v>16.53585231050533</v>
+        <v>16.53585231050532</v>
       </c>
       <c r="AU4" t="n">
         <v>0.8775874376296997</v>
       </c>
       <c r="AV4" t="n">
-        <v>80.02205498524854</v>
+        <v>9.197693682731465</v>
       </c>
       <c r="AW4" t="n">
-        <v>70.12296455747779</v>
+        <v>-0.1649947876625895</v>
       </c>
       <c r="AX4" t="n">
-        <v>92.04406578064125</v>
+        <v>6.786482384864321</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.197693682731465</v>
+        <v>0.8713752665418273</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.1649947876625895</v>
+        <v>3.478934917044132</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.786482384864321</v>
+        <v>-0.2578502005719123</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.8713752665418273</v>
+        <v>2.079888607593293</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.478934917044132</v>
+        <v>0.4209843087703629</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.2578502005719123</v>
+        <v>1.715071657870677</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.079888607593293</v>
+        <v>0.4157685218973359</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.4209843087703629</v>
+        <v>80.02205498524857</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.715071657870677</v>
+        <v>70.1229645574778</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.4157685218973359</v>
+        <v>92.04406578064116</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.7431702748352507</v>
+        <v>0.7431702748352009</v>
       </c>
       <c r="BJ4" t="n">
-        <v>6.505908929022169</v>
+        <v>6.505908929022116</v>
       </c>
       <c r="BK4" t="n">
-        <v>11.72056172985108</v>
+        <v>11.72056172985113</v>
       </c>
       <c r="BL4" t="n">
-        <v>7.89882934004563</v>
+        <v>7.898829340045616</v>
       </c>
       <c r="BM4" t="n">
-        <v>-7.567819865472067</v>
+        <v>-7.567819865472053</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.52113450015041</v>
+        <v>6.521134500150453</v>
       </c>
     </row>
     <row r="5">
@@ -1371,7 +1371,7 @@
         <v>124.8772966100815</v>
       </c>
       <c r="D5" t="n">
-        <v>2.440984198387639</v>
+        <v>2.440984198387633</v>
       </c>
       <c r="E5" t="n">
         <v>0.999934196472168</v>
@@ -1380,7 +1380,7 @@
         <v>107.5047675599443</v>
       </c>
       <c r="G5" t="n">
-        <v>12.58023850461268</v>
+        <v>12.5802385046127</v>
       </c>
       <c r="H5" t="n">
         <v>0.9996181726455688</v>
@@ -1389,7 +1389,7 @@
         <v>87.57902104803857</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3269439047955416</v>
+        <v>-0.3269439047955452</v>
       </c>
       <c r="K5" t="n">
         <v>0.9990646243095398</v>
@@ -1398,7 +1398,7 @@
         <v>84.44120528850151</v>
       </c>
       <c r="M5" t="n">
-        <v>2.879723082197472</v>
+        <v>2.879723082197474</v>
       </c>
       <c r="N5" t="n">
         <v>0.9993699193000793</v>
@@ -1416,7 +1416,7 @@
         <v>95.08938079184675</v>
       </c>
       <c r="S5" t="n">
-        <v>14.75994028943649</v>
+        <v>14.7599402894365</v>
       </c>
       <c r="T5" t="n">
         <v>0.9902499318122864</v>
@@ -1434,7 +1434,7 @@
         <v>51.65768075496592</v>
       </c>
       <c r="Y5" t="n">
-        <v>28.46286043207695</v>
+        <v>28.46286043207696</v>
       </c>
       <c r="Z5" t="n">
         <v>0.9890871047973633</v>
@@ -1461,7 +1461,7 @@
         <v>52.27275604897358</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.717416966215097</v>
+        <v>4.717416966215094</v>
       </c>
       <c r="AI5" t="n">
         <v>0.9973756074905396</v>
@@ -1470,7 +1470,7 @@
         <v>62.78927985658037</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.717831226105375</v>
+        <v>1.717831226105386</v>
       </c>
       <c r="AL5" t="n">
         <v>0.9979268312454224</v>
@@ -1479,7 +1479,7 @@
         <v>34.14132544334899</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.581159875748</v>
+        <v>23.58115987574801</v>
       </c>
       <c r="AO5" t="n">
         <v>0.999545156955719</v>
@@ -1488,7 +1488,7 @@
         <v>22.69794788766415</v>
       </c>
       <c r="AQ5" t="n">
-        <v>28.96628684185922</v>
+        <v>28.96628684185921</v>
       </c>
       <c r="AR5" t="n">
         <v>0.8922911882400513</v>
@@ -1503,61 +1503,61 @@
         <v>0.9834632277488708</v>
       </c>
       <c r="AV5" t="n">
-        <v>84.1941569112245</v>
+        <v>8.408791968163023</v>
       </c>
       <c r="AW5" t="n">
-        <v>90.09788936108571</v>
+        <v>-1.960765554549845</v>
       </c>
       <c r="AX5" t="n">
-        <v>88.55518780912922</v>
+        <v>6.992658655694193</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.408791968163023</v>
+        <v>-0.770780888009579</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1.960765554549845</v>
+        <v>3.188849510030543</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.992658655694193</v>
+        <v>-0.6395147201862734</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.770780888009579</v>
+        <v>2.533604236359292</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.188849510030543</v>
+        <v>-0.2493797464573646</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.6395147201862734</v>
+        <v>2.175832302012342</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.533604236359292</v>
+        <v>-0.146842510142223</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.2493797464573646</v>
+        <v>84.19415691122443</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.175832302012342</v>
+        <v>90.09788936108572</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.146842510142223</v>
+        <v>88.55518780912925</v>
       </c>
       <c r="BI5" t="n">
-        <v>10.15820142258643</v>
+        <v>10.15820142258637</v>
       </c>
       <c r="BJ5" t="n">
-        <v>6.926730278153713</v>
+        <v>6.926730278153769</v>
       </c>
       <c r="BK5" t="n">
-        <v>17.89012090013307</v>
+        <v>17.89012090013309</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.1052654896385938</v>
+        <v>-0.1052654896386223</v>
       </c>
       <c r="BM5" t="n">
-        <v>-1.549750588091449</v>
+        <v>-1.549750588091392</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.614250119227865</v>
+        <v>2.614250119227854</v>
       </c>
     </row>
     <row r="6">
@@ -1571,7 +1571,7 @@
         <v>125.8899282901845</v>
       </c>
       <c r="D6" t="n">
-        <v>3.239570780003334</v>
+        <v>3.239570780003325</v>
       </c>
       <c r="E6" t="n">
         <v>0.9996028542518616</v>
@@ -1589,7 +1589,7 @@
         <v>87.63461823159076</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1956209223321252</v>
+        <v>-0.1956209223321144</v>
       </c>
       <c r="K6" t="n">
         <v>0.9991750121116638</v>
@@ -1598,7 +1598,7 @@
         <v>84.70872919610207</v>
       </c>
       <c r="M6" t="n">
-        <v>2.995608715300847</v>
+        <v>2.995608715300865</v>
       </c>
       <c r="N6" t="n">
         <v>0.998900294303894</v>
@@ -1607,7 +1607,7 @@
         <v>86.08625696060506</v>
       </c>
       <c r="P6" t="n">
-        <v>12.49594181141956</v>
+        <v>12.49594181141955</v>
       </c>
       <c r="Q6" t="n">
         <v>0.9779728651046753</v>
@@ -1616,7 +1616,7 @@
         <v>95.49360883996842</v>
       </c>
       <c r="S6" t="n">
-        <v>14.87207615629154</v>
+        <v>14.87207615629156</v>
       </c>
       <c r="T6" t="n">
         <v>0.9909895658493042</v>
@@ -1625,7 +1625,7 @@
         <v>93.26981077802942</v>
       </c>
       <c r="V6" t="n">
-        <v>24.10252347905586</v>
+        <v>24.10252347905585</v>
       </c>
       <c r="W6" t="n">
         <v>0.9475305080413818</v>
@@ -1634,7 +1634,7 @@
         <v>53.68334181765293</v>
       </c>
       <c r="Y6" t="n">
-        <v>28.90266256129487</v>
+        <v>28.90266256129488</v>
       </c>
       <c r="Z6" t="n">
         <v>0.9921683669090271</v>
@@ -1643,7 +1643,7 @@
         <v>50.34196731892038</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.8649467305934</v>
+        <v>19.86494673059342</v>
       </c>
       <c r="AC6" t="n">
         <v>0.9722821116447449</v>
@@ -1652,7 +1652,7 @@
         <v>59.73250612299493</v>
       </c>
       <c r="AE6" t="n">
-        <v>16.58844643450797</v>
+        <v>16.58844643450798</v>
       </c>
       <c r="AF6" t="n">
         <v>0.9971601963043213</v>
@@ -1661,7 +1661,7 @@
         <v>58.98019506576214</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.664414426113694</v>
+        <v>3.664414426113697</v>
       </c>
       <c r="AI6" t="n">
         <v>0.9971465468406677</v>
@@ -1670,7 +1670,7 @@
         <v>70.16885635700632</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.9431392588513745</v>
+        <v>0.9431392588513964</v>
       </c>
       <c r="AL6" t="n">
         <v>0.9966065883636475</v>
@@ -1679,7 +1679,7 @@
         <v>35.34953340570978</v>
       </c>
       <c r="AN6" t="n">
-        <v>22.87471040766289</v>
+        <v>22.8747104076629</v>
       </c>
       <c r="AO6" t="n">
         <v>0.9990921020507812</v>
@@ -1688,7 +1688,7 @@
         <v>25.08211744592545</v>
       </c>
       <c r="AQ6" t="n">
-        <v>29.66142208018201</v>
+        <v>29.66142208018202</v>
       </c>
       <c r="AR6" t="n">
         <v>0.8451337218284607</v>
@@ -1697,67 +1697,67 @@
         <v>16.77293676011106</v>
       </c>
       <c r="AT6" t="n">
-        <v>14.95004207529919</v>
+        <v>14.9500420752992</v>
       </c>
       <c r="AU6" t="n">
         <v>0.967080295085907</v>
       </c>
       <c r="AV6" t="n">
-        <v>100.3384578304214</v>
+        <v>5.276162573631776</v>
       </c>
       <c r="AW6" t="n">
-        <v>105.9032063577439</v>
+        <v>-3.229718512677131</v>
       </c>
       <c r="AX6" t="n">
-        <v>88.94456460445835</v>
+        <v>5.244920608845163</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.276162573631776</v>
+        <v>-2.06540290345537</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-3.229718512677131</v>
+        <v>2.199905476671585</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.244920608845163</v>
+        <v>-0.6275552384396814</v>
       </c>
       <c r="BB6" t="n">
-        <v>-2.06540290345537</v>
+        <v>1.581129114678564</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.199905476671585</v>
+        <v>-0.873726986824197</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.6275552384396814</v>
+        <v>1.421386637586231</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.581129114678564</v>
+        <v>-0.7003976943645078</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.873726986824197</v>
+        <v>100.3384578304213</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.421386637586231</v>
+        <v>105.903206357744</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.7003976943645078</v>
+        <v>88.94456460445838</v>
       </c>
       <c r="BI6" t="n">
-        <v>14.59663083114268</v>
+        <v>14.59663083114274</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-1.279352173831832</v>
+        <v>-1.279352173831764</v>
       </c>
       <c r="BK6" t="n">
-        <v>11.51003075057389</v>
+        <v>11.51003075057388</v>
       </c>
       <c r="BL6" t="n">
-        <v>-9.493552192282333</v>
+        <v>-9.493552192282351</v>
       </c>
       <c r="BM6" t="n">
-        <v>-2.339319627016337</v>
+        <v>-2.339319627016344</v>
       </c>
       <c r="BN6" t="n">
-        <v>-1.671357548640927</v>
+        <v>-1.671357548640952</v>
       </c>
     </row>
     <row r="7">
@@ -1771,7 +1771,7 @@
         <v>126.8979336353059</v>
       </c>
       <c r="D7" t="n">
-        <v>2.815636168134972</v>
+        <v>2.815636168134974</v>
       </c>
       <c r="E7" t="n">
         <v>0.9995899796485901</v>
@@ -1789,7 +1789,7 @@
         <v>87.52142723570479</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.532953789893611</v>
+        <v>-0.5329537898936171</v>
       </c>
       <c r="K7" t="n">
         <v>0.9985741376876831</v>
@@ -1798,7 +1798,7 @@
         <v>84.73833773998504</v>
       </c>
       <c r="M7" t="n">
-        <v>2.740429817362042</v>
+        <v>2.740429817362035</v>
       </c>
       <c r="N7" t="n">
         <v>0.9989545345306396</v>
@@ -1807,7 +1807,7 @@
         <v>87.15490787587268</v>
       </c>
       <c r="P7" t="n">
-        <v>12.27868262757647</v>
+        <v>12.27868262757646</v>
       </c>
       <c r="Q7" t="n">
         <v>0.9689679145812988</v>
@@ -1816,7 +1816,7 @@
         <v>96.85375944096992</v>
       </c>
       <c r="S7" t="n">
-        <v>14.44864475980719</v>
+        <v>14.44864475980718</v>
       </c>
       <c r="T7" t="n">
         <v>0.9883636236190796</v>
@@ -1834,7 +1834,7 @@
         <v>54.50045403013839</v>
       </c>
       <c r="Y7" t="n">
-        <v>28.23338610060671</v>
+        <v>28.23338610060672</v>
       </c>
       <c r="Z7" t="n">
         <v>0.992194652557373</v>
@@ -1861,7 +1861,7 @@
         <v>62.7625972666639</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.884481876454458</v>
+        <v>3.884481876454455</v>
       </c>
       <c r="AI7" t="n">
         <v>0.9950264096260071</v>
@@ -1870,7 +1870,7 @@
         <v>73.34160500384392</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.9182869119847226</v>
+        <v>0.9182869119847075</v>
       </c>
       <c r="AL7" t="n">
         <v>0.9982301592826843</v>
@@ -1879,7 +1879,7 @@
         <v>36.26234987948803</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.5934104107796</v>
+        <v>21.59341041077959</v>
       </c>
       <c r="AO7" t="n">
         <v>0.9988743662834167</v>
@@ -1888,7 +1888,7 @@
         <v>27.77102653016436</v>
       </c>
       <c r="AQ7" t="n">
-        <v>28.55304961508892</v>
+        <v>28.55304961508893</v>
       </c>
       <c r="AR7" t="n">
         <v>0.3957178890705109</v>
@@ -1897,67 +1897,67 @@
         <v>21.54175778652759</v>
       </c>
       <c r="AT7" t="n">
-        <v>13.57751399912732</v>
+        <v>13.57751399912733</v>
       </c>
       <c r="AU7" t="n">
         <v>0.9506142735481262</v>
       </c>
       <c r="AV7" t="n">
-        <v>113.3874185735098</v>
+        <v>1.94935494280876</v>
       </c>
       <c r="AW7" t="n">
+        <v>-2.445432987618956</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.861852848783453</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-1.976542777203498</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.933739033151181</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0.4096731226494974</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.7861502627108976</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0.4326617464106111</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.7750369132833264</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0.6405840528772249</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>113.3874185735099</v>
+      </c>
+      <c r="BG7" t="n">
         <v>113.1179508622335</v>
       </c>
-      <c r="AX7" t="n">
-        <v>83.87654855509655</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.94935494280876</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-2.445432987618956</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.861852848783453</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-1.976542777203498</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.933739033151181</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-0.4096731226494974</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.7861502627108976</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>-0.4326617464106111</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0.7750369132833264</v>
-      </c>
       <c r="BH7" t="n">
-        <v>-0.6405840528772249</v>
+        <v>83.87654855509656</v>
       </c>
       <c r="BI7" t="n">
-        <v>7.599497074922766</v>
+        <v>7.599497074922844</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-5.859806883765589</v>
+        <v>-5.859806883765636</v>
       </c>
       <c r="BK7" t="n">
-        <v>-1.096983484431597</v>
+        <v>-1.096983484431611</v>
       </c>
       <c r="BL7" t="n">
-        <v>-8.023304120715402</v>
+        <v>-8.023304120715416</v>
       </c>
       <c r="BM7" t="n">
-        <v>-4.892465685373303</v>
+        <v>-4.892465685373296</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.738202393050333</v>
+        <v>0.7382023930503188</v>
       </c>
     </row>
     <row r="8">
@@ -1971,7 +1971,7 @@
         <v>127.6138143336519</v>
       </c>
       <c r="D8" t="n">
-        <v>2.828119156208459</v>
+        <v>2.828119156208444</v>
       </c>
       <c r="E8" t="n">
         <v>0.9998170733451843</v>
@@ -1980,7 +1980,7 @@
         <v>110.4557037353516</v>
       </c>
       <c r="G8" t="n">
-        <v>12.37357930934175</v>
+        <v>12.37357930934176</v>
       </c>
       <c r="H8" t="n">
         <v>0.9994544386863708</v>
@@ -1998,7 +1998,7 @@
         <v>84.59969378532247</v>
       </c>
       <c r="M8" t="n">
-        <v>2.830911189951792</v>
+        <v>2.830911189951796</v>
       </c>
       <c r="N8" t="n">
         <v>0.9992908239364624</v>
@@ -2016,7 +2016,7 @@
         <v>97.41114352611785</v>
       </c>
       <c r="S8" t="n">
-        <v>14.64743106923206</v>
+        <v>14.64743106923205</v>
       </c>
       <c r="T8" t="n">
         <v>0.9870042204856873</v>
@@ -2034,7 +2034,7 @@
         <v>55.23341564421958</v>
       </c>
       <c r="Y8" t="n">
-        <v>27.36593205878074</v>
+        <v>27.36593205878075</v>
       </c>
       <c r="Z8" t="n">
         <v>0.9880083799362183</v>
@@ -2070,7 +2070,7 @@
         <v>74.06756624262384</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.4570981289478198</v>
+        <v>0.4570981289478059</v>
       </c>
       <c r="AL8" t="n">
         <v>0.9977892637252808</v>
@@ -2079,7 +2079,7 @@
         <v>37.06118401060714</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.4153643668966</v>
+        <v>19.41536436689661</v>
       </c>
       <c r="AO8" t="n">
         <v>0.9988911747932434</v>
@@ -2088,7 +2088,7 @@
         <v>28.83299969612284</v>
       </c>
       <c r="AQ8" t="n">
-        <v>26.73229461020611</v>
+        <v>26.73229461020612</v>
       </c>
       <c r="AR8" t="n">
         <v>0.332738846540451</v>
@@ -2097,67 +2097,67 @@
         <v>28.77762165475399</v>
       </c>
       <c r="AT8" t="n">
-        <v>26.51301444844998</v>
+        <v>26.51301444844997</v>
       </c>
       <c r="AU8" t="n">
         <v>0.5457343459129333</v>
       </c>
       <c r="AV8" t="n">
-        <v>115.5374519802669</v>
+        <v>0.3852965983938645</v>
       </c>
       <c r="AW8" t="n">
-        <v>103.7092393888807</v>
+        <v>-0.9614721257635885</v>
       </c>
       <c r="AX8" t="n">
-        <v>79.15963323371174</v>
+        <v>1.291835054438167</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.3852965983938645</v>
+        <v>-1.221931741592732</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.9614721257635885</v>
+        <v>1.38055923137259</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.291835054438167</v>
+        <v>-0.8465320505994427</v>
       </c>
       <c r="BB8" t="n">
-        <v>-1.221931741592732</v>
+        <v>0.7158056218573421</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.38055923137259</v>
+        <v>-0.1127151732749141</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.8465320505994427</v>
+        <v>0.1402185318317812</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.7158056218573421</v>
+        <v>-0.2701089737263125</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.1127151732749141</v>
+        <v>115.537451980267</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.1402185318317812</v>
+        <v>103.7092393888808</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.2701089737263125</v>
+        <v>79.15963323371179</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.877017063611497</v>
+        <v>2.877017063611468</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-2.822614976006687</v>
+        <v>-2.822614976006751</v>
       </c>
       <c r="BK8" t="n">
-        <v>-4.536577490856914</v>
+        <v>-4.536577490856949</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0307251203643446</v>
+        <v>0.0307251203643375</v>
       </c>
       <c r="BM8" t="n">
-        <v>-0.8629148409156713</v>
+        <v>-0.8629148409157068</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.384863067861062</v>
+        <v>2.384863067861037</v>
       </c>
     </row>
     <row r="9">
@@ -2171,7 +2171,7 @@
         <v>128.3709505771069</v>
       </c>
       <c r="D9" t="n">
-        <v>2.900874361078792</v>
+        <v>2.90087436107879</v>
       </c>
       <c r="E9" t="n">
         <v>0.9999250173568726</v>
@@ -2180,7 +2180,7 @@
         <v>111.2513765375665</v>
       </c>
       <c r="G9" t="n">
-        <v>12.37273520611703</v>
+        <v>12.37273520611702</v>
       </c>
       <c r="H9" t="n">
         <v>0.9995716214179993</v>
@@ -2189,7 +2189,7 @@
         <v>87.70015797716506</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4814797259391526</v>
+        <v>-0.4814797259391623</v>
       </c>
       <c r="K9" t="n">
         <v>0.9979802966117859</v>
@@ -2198,7 +2198,7 @@
         <v>84.72951523801115</v>
       </c>
       <c r="M9" t="n">
-        <v>3.042261651221736</v>
+        <v>3.042261651221742</v>
       </c>
       <c r="N9" t="n">
         <v>0.998928964138031</v>
@@ -2216,7 +2216,7 @@
         <v>97.66027572307182</v>
       </c>
       <c r="S9" t="n">
-        <v>14.75477827356218</v>
+        <v>14.75477827356217</v>
       </c>
       <c r="T9" t="n">
         <v>0.9771835803985596</v>
@@ -2225,7 +2225,7 @@
         <v>95.43328792490858</v>
       </c>
       <c r="V9" t="n">
-        <v>24.11852897481717</v>
+        <v>24.11852897481716</v>
       </c>
       <c r="W9" t="n">
         <v>0.9659965634346008</v>
@@ -2243,7 +2243,7 @@
         <v>52.33388454356093</v>
       </c>
       <c r="AB9" t="n">
-        <v>17.31979694772275</v>
+        <v>17.31979694772274</v>
       </c>
       <c r="AC9" t="n">
         <v>0.940184473991394</v>
@@ -2261,7 +2261,7 @@
         <v>65.34626737554024</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.563657720038236</v>
+        <v>3.563657720038232</v>
       </c>
       <c r="AI9" t="n">
         <v>0.9963681697845459</v>
@@ -2270,7 +2270,7 @@
         <v>74.11219820063165</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.008424799493013779</v>
+        <v>-0.008424799493018617</v>
       </c>
       <c r="AL9" t="n">
         <v>0.9983150959014893</v>
@@ -2288,7 +2288,7 @@
         <v>30.74493611112554</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25.1700299851438</v>
+        <v>25.17002998514378</v>
       </c>
       <c r="AR9" t="n">
         <v>0.1551168262958527</v>
@@ -2297,67 +2297,67 @@
         <v>29.24704856060921</v>
       </c>
       <c r="AT9" t="n">
-        <v>25.97453340570976</v>
+        <v>25.97453340570977</v>
       </c>
       <c r="AU9" t="n">
         <v>0.9216576218605042</v>
       </c>
       <c r="AV9" t="n">
+        <v>0.02641069128158335</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.09978274081615623</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.4179893655979896</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.4979214769728664</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.2406749319522952</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.5015271775265955</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.5607199161610694</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.03253348330233763</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.2348189658307014</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.367524776052921</v>
+      </c>
+      <c r="BF9" t="n">
         <v>119.1414527007328</v>
       </c>
-      <c r="AW9" t="n">
-        <v>104.0447958805197</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>82.15071887326521</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.02641069128158335</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-0.09978274081615623</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.4179893655979896</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-0.4979214769728664</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.2406749319522952</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>-0.5015271775265955</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.5607199161610694</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0.03253348330233763</v>
-      </c>
       <c r="BG9" t="n">
-        <v>0.2348189658307014</v>
+        <v>104.0447958805196</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.367524776052921</v>
+        <v>82.15071887326515</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.954267122909393</v>
+        <v>1.954267122909343</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-1.563422113333019</v>
+        <v>-1.563422113332969</v>
       </c>
       <c r="BK9" t="n">
-        <v>-1.035533243702908</v>
+        <v>-1.035533243702936</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.895247168616795</v>
+        <v>1.895247168616823</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.1227395496511789</v>
+        <v>-0.1227395496512216</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.009897338840826109</v>
+        <v>0.009897338840847425</v>
       </c>
     </row>
     <row r="10">
@@ -2371,7 +2371,7 @@
         <v>129.055153055394</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725398286860042</v>
+        <v>2.72539828686004</v>
       </c>
       <c r="E10" t="n">
         <v>0.9999117851257324</v>
@@ -2380,7 +2380,7 @@
         <v>112.3271455156042</v>
       </c>
       <c r="G10" t="n">
-        <v>12.74120249646774</v>
+        <v>12.74120249646775</v>
       </c>
       <c r="H10" t="n">
         <v>0.9995716214179993</v>
@@ -2389,7 +2389,7 @@
         <v>88.01063375270114</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4441930892619723</v>
+        <v>-0.4441930892619681</v>
       </c>
       <c r="K10" t="n">
         <v>0.9992737174034119</v>
@@ -2398,7 +2398,7 @@
         <v>86.0225758654006</v>
       </c>
       <c r="M10" t="n">
-        <v>3.226211223196458</v>
+        <v>3.226211223196476</v>
       </c>
       <c r="N10" t="n">
         <v>0.9996641874313354</v>
@@ -2407,7 +2407,7 @@
         <v>89.82473332831201</v>
       </c>
       <c r="P10" t="n">
-        <v>12.42089778818982</v>
+        <v>12.42089778818983</v>
       </c>
       <c r="Q10" t="n">
         <v>0.9868425726890564</v>
@@ -2416,7 +2416,7 @@
         <v>99.11206022221992</v>
       </c>
       <c r="S10" t="n">
-        <v>15.04729250644115</v>
+        <v>15.04729250644116</v>
       </c>
       <c r="T10" t="n">
         <v>0.9903680086135864</v>
@@ -2443,7 +2443,7 @@
         <v>53.03570767666432</v>
       </c>
       <c r="AB10" t="n">
-        <v>17.12695182637964</v>
+        <v>17.12695182637966</v>
       </c>
       <c r="AC10" t="n">
         <v>0.9364562034606934</v>
@@ -2452,7 +2452,7 @@
         <v>64.08133405320189</v>
       </c>
       <c r="AE10" t="n">
-        <v>16.15995041867518</v>
+        <v>16.1599504186752</v>
       </c>
       <c r="AF10" t="n">
         <v>0.9959445595741272</v>
@@ -2461,7 +2461,7 @@
         <v>65.53987949452502</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.621024273811486</v>
+        <v>3.621024273811503</v>
       </c>
       <c r="AI10" t="n">
         <v>0.9952091574668884</v>
@@ -2470,7 +2470,7 @@
         <v>74.12038762518701</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.01215833298701341</v>
+        <v>0.01215833298703457</v>
       </c>
       <c r="AL10" t="n">
         <v>0.9982366561889648</v>
@@ -2497,67 +2497,67 @@
         <v>30.03444874540289</v>
       </c>
       <c r="AT10" t="n">
-        <v>25.52708564920627</v>
+        <v>25.52708564920628</v>
       </c>
       <c r="AU10" t="n">
         <v>0.8771986961364746</v>
       </c>
       <c r="AV10" t="n">
+        <v>0.1857311167615521</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.0606029591661823</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.295992100492434</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.07069263052433072</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.3775048763193993</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.1923916187692196</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.7808725884620173</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.2525289007957952</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.8752680839376232</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.3423224104211684</v>
+      </c>
+      <c r="BF10" t="n">
         <v>119.4459862260857</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BG10" t="n">
         <v>101.6381729014749</v>
       </c>
-      <c r="AX10" t="n">
-        <v>78.91415413440939</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.1857311167615521</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.0606029591661823</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.295992100492434</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-0.07069263052433072</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.3775048763193993</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0.1923916187692196</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.7808725884620173</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0.2525289007957952</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0.8752680839376232</v>
-      </c>
       <c r="BH10" t="n">
-        <v>0.3423224104211684</v>
+        <v>78.91415413440934</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0.2498271630545403</v>
+        <v>-0.2498271630544693</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-1.97716103723014</v>
+        <v>-1.977161037230093</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0.7460831536233243</v>
+        <v>-0.746083153623303</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.246394549063936</v>
+        <v>1.246394549063954</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.8431201632340191</v>
+        <v>-0.843120163234012</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.885264501292649</v>
+        <v>1.885264501292685</v>
       </c>
     </row>
     <row r="11">
@@ -2571,7 +2571,7 @@
         <v>130.1232520570146</v>
       </c>
       <c r="D11" t="n">
-        <v>3.116575200506986</v>
+        <v>3.116575200506982</v>
       </c>
       <c r="E11" t="n">
         <v>0.9996154308319092</v>
@@ -2580,7 +2580,7 @@
         <v>113.0242692663315</v>
       </c>
       <c r="G11" t="n">
-        <v>12.81486673558013</v>
+        <v>12.81486673558012</v>
       </c>
       <c r="H11" t="n">
         <v>0.9983939528465271</v>
@@ -2589,7 +2589,7 @@
         <v>88.69560728681849</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6534008269614446</v>
+        <v>-0.6534008269614362</v>
       </c>
       <c r="K11" t="n">
         <v>0.9986023306846619</v>
@@ -2598,7 +2598,7 @@
         <v>87.89793785582198</v>
       </c>
       <c r="M11" t="n">
-        <v>3.241892063871347</v>
+        <v>3.241892063871343</v>
       </c>
       <c r="N11" t="n">
         <v>0.9984007477760315</v>
@@ -2607,7 +2607,7 @@
         <v>90.81209060993601</v>
       </c>
       <c r="P11" t="n">
-        <v>12.4692551633145</v>
+        <v>12.46925516331449</v>
       </c>
       <c r="Q11" t="n">
         <v>0.9925597906112671</v>
@@ -2616,7 +2616,7 @@
         <v>99.64301738333195</v>
       </c>
       <c r="S11" t="n">
-        <v>15.16223663979389</v>
+        <v>15.16223663979388</v>
       </c>
       <c r="T11" t="n">
         <v>0.9918648600578308</v>
@@ -2625,7 +2625,7 @@
         <v>97.40485333381815</v>
       </c>
       <c r="V11" t="n">
-        <v>23.99412114569481</v>
+        <v>23.99412114569482</v>
       </c>
       <c r="W11" t="n">
         <v>0.9463396072387695</v>
@@ -2634,7 +2634,7 @@
         <v>56.53142726167719</v>
       </c>
       <c r="Y11" t="n">
-        <v>26.18652506077544</v>
+        <v>26.18652506077543</v>
       </c>
       <c r="Z11" t="n">
         <v>0.9886445999145508</v>
@@ -2643,7 +2643,7 @@
         <v>53.89562972048496</v>
       </c>
       <c r="AB11" t="n">
-        <v>16.93373335168718</v>
+        <v>16.93373335168717</v>
       </c>
       <c r="AC11" t="n">
         <v>0.9581555724143982</v>
@@ -2652,7 +2652,7 @@
         <v>64.59392791098738</v>
       </c>
       <c r="AE11" t="n">
-        <v>15.7403661849651</v>
+        <v>15.74036618496509</v>
       </c>
       <c r="AF11" t="n">
         <v>0.9955859184265137</v>
@@ -2661,7 +2661,7 @@
         <v>65.9382515765251</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.340960563497333</v>
+        <v>3.340960563497341</v>
       </c>
       <c r="AI11" t="n">
         <v>0.9931269884109497</v>
@@ -2670,7 +2670,7 @@
         <v>74.48366043415476</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.1906374667553052</v>
+        <v>-0.1906374667553191</v>
       </c>
       <c r="AL11" t="n">
         <v>0.9981417655944824</v>
@@ -2703,61 +2703,61 @@
         <v>0.9695777297019958</v>
       </c>
       <c r="AV11" t="n">
-        <v>118.6417983746238</v>
+        <v>0.147616609613948</v>
       </c>
       <c r="AW11" t="n">
+        <v>-0.1280358497132639</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.2766041045493282</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.05790426376017876</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.6254581694907344</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.1092687566229635</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.06577771775266</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.0488687068858038</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.9194637866730382</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.06282177377254605</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>118.6417983746239</v>
+      </c>
+      <c r="BG11" t="n">
         <v>102.552629573273</v>
       </c>
-      <c r="AX11" t="n">
-        <v>80.46447854679717</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0.147616609613948</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-0.1280358497132639</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0.2766041045493282</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>-0.05790426376017876</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0.6254581694907344</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0.1092687566229635</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.06577771775266</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0.0488687068858038</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0.9194637866730382</v>
-      </c>
       <c r="BH11" t="n">
-        <v>0.06282177377254605</v>
+        <v>80.46447854679712</v>
       </c>
       <c r="BI11" t="n">
-        <v>-2.000054951550887</v>
+        <v>-2.000054951550844</v>
       </c>
       <c r="BJ11" t="n">
-        <v>-1.295757888827353</v>
+        <v>-1.295757888827424</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.457255854424965</v>
+        <v>1.457255854424972</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5955246144127386</v>
+        <v>0.5955246144126995</v>
       </c>
       <c r="BM11" t="n">
-        <v>3.64778945293412</v>
+        <v>3.647789452934148</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.138163560140882</v>
+        <v>1.13816356014086</v>
       </c>
     </row>
     <row r="12">
@@ -2771,7 +2771,7 @@
         <v>131.3843585075216</v>
       </c>
       <c r="D12" t="n">
-        <v>3.154787104180514</v>
+        <v>3.154787104180519</v>
       </c>
       <c r="E12" t="n">
         <v>0.9993937015533447</v>
@@ -2780,7 +2780,7 @@
         <v>114.4593583776596</v>
       </c>
       <c r="G12" t="n">
-        <v>12.17816941281583</v>
+        <v>12.17816941281582</v>
       </c>
       <c r="H12" t="n">
         <v>0.9992021918296814</v>
@@ -2789,7 +2789,7 @@
         <v>89.55994463981466</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.734258773479041</v>
+        <v>-1.734258773479056</v>
       </c>
       <c r="K12" t="n">
         <v>0.9991520643234253</v>
@@ -2798,7 +2798,7 @@
         <v>91.84429087537401</v>
       </c>
       <c r="M12" t="n">
-        <v>2.581770876620681</v>
+        <v>2.581770876620678</v>
       </c>
       <c r="N12" t="n">
         <v>0.9960349202156067</v>
@@ -2807,7 +2807,7 @@
         <v>91.58292729803857</v>
       </c>
       <c r="P12" t="n">
-        <v>12.76508087807514</v>
+        <v>12.76508087807513</v>
       </c>
       <c r="Q12" t="n">
         <v>0.9892011880874634</v>
@@ -2825,7 +2825,7 @@
         <v>98.39598473082198</v>
       </c>
       <c r="V12" t="n">
-        <v>23.59861008664396</v>
+        <v>23.59861008664395</v>
       </c>
       <c r="W12" t="n">
         <v>0.9706884622573853</v>
@@ -2834,7 +2834,7 @@
         <v>57.54198114922706</v>
       </c>
       <c r="Y12" t="n">
-        <v>26.24812024704951</v>
+        <v>26.24812024704953</v>
       </c>
       <c r="Z12" t="n">
         <v>0.9828534722328186</v>
@@ -2861,7 +2861,7 @@
         <v>66.09308770362368</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.304923848902916</v>
+        <v>3.304923848902926</v>
       </c>
       <c r="AI12" t="n">
         <v>0.993791401386261</v>
@@ -2870,7 +2870,7 @@
         <v>74.4156208444149</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.02326153694315281</v>
+        <v>-0.0232615369431516</v>
       </c>
       <c r="AL12" t="n">
         <v>0.9972777962684631</v>
@@ -2879,7 +2879,7 @@
         <v>40.04766180160198</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.13872317050365</v>
+        <v>18.13872317050366</v>
       </c>
       <c r="AO12" t="n">
         <v>0.9981270432472229</v>
@@ -2888,7 +2888,7 @@
         <v>31.43638245602872</v>
       </c>
       <c r="AQ12" t="n">
-        <v>23.83797016549616</v>
+        <v>23.83797016549618</v>
       </c>
       <c r="AR12" t="n">
         <v>0.1204911842942238</v>
@@ -2903,61 +2903,61 @@
         <v>0.9859428405761719</v>
       </c>
       <c r="AV12" t="n">
-        <v>115.4458763229839</v>
+        <v>-0.07034058266497567</v>
       </c>
       <c r="AW12" t="n">
+        <v>-0.1240466503386841</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.1801835729720764</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.01035751180446098</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.5960423895653264</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.1475435622194965</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.878610002233625</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.2178709557715894</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.000911631482715</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0.002061559798869794</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>115.445876322984</v>
+      </c>
+      <c r="BG12" t="n">
         <v>104.5526846103248</v>
       </c>
-      <c r="AX12" t="n">
-        <v>86.20973304027763</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-0.07034058266497567</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-0.1240466503386841</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.1801835729720764</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-0.01035751180446098</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.5960423895653264</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0.1475435622194965</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0.878610002233625</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>-0.2178709557715894</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.000911631482715</v>
-      </c>
       <c r="BH12" t="n">
-        <v>-0.002061559798869794</v>
+        <v>86.20973304027764</v>
       </c>
       <c r="BI12" t="n">
-        <v>-2.841342940709247</v>
+        <v>-2.841342940709318</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-0.5389009146855095</v>
+        <v>-0.5389009146855557</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4449660752021529</v>
+        <v>0.4449660752020961</v>
       </c>
       <c r="BL12" t="n">
-        <v>-2.541285083838407</v>
+        <v>-2.54128508383841</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.433206957047744</v>
+        <v>1.433206957047709</v>
       </c>
       <c r="BN12" t="n">
-        <v>-2.795546326881585</v>
+        <v>-2.795546326881599</v>
       </c>
     </row>
     <row r="13">
@@ -2971,7 +2971,7 @@
         <v>132.5133952688664</v>
       </c>
       <c r="D13" t="n">
-        <v>4.295982198512291</v>
+        <v>4.2959821985123</v>
       </c>
       <c r="E13" t="n">
         <v>0.9997614026069641</v>
@@ -2980,7 +2980,7 @@
         <v>115.5520824675864</v>
       </c>
       <c r="G13" t="n">
-        <v>12.73454706719582</v>
+        <v>12.73454706719581</v>
       </c>
       <c r="H13" t="n">
         <v>0.9996390342712402</v>
@@ -2989,7 +2989,7 @@
         <v>95.11373803970662</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.73101222261468</v>
+        <v>-1.731012222614694</v>
       </c>
       <c r="K13" t="n">
         <v>0.9996263980865479</v>
@@ -2998,7 +2998,7 @@
         <v>97.08855811585772</v>
       </c>
       <c r="M13" t="n">
-        <v>3.043527806058847</v>
+        <v>3.043527806058843</v>
       </c>
       <c r="N13" t="n">
         <v>0.9963145852088928</v>
@@ -3043,7 +3043,7 @@
         <v>55.65284972495221</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.16047246405421</v>
+        <v>17.16047246405419</v>
       </c>
       <c r="AC13" t="n">
         <v>0.9739347100257874</v>
@@ -3052,7 +3052,7 @@
         <v>65.78601269011803</v>
       </c>
       <c r="AE13" t="n">
-        <v>15.18195943629487</v>
+        <v>15.18195943629488</v>
       </c>
       <c r="AF13" t="n">
         <v>0.993826687335968</v>
@@ -3061,7 +3061,7 @@
         <v>66.29861872246926</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.923340493060181</v>
+        <v>2.923340493060173</v>
       </c>
       <c r="AI13" t="n">
         <v>0.9923794269561768</v>
@@ -3070,7 +3070,7 @@
         <v>74.34297926882481</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.09466942320477756</v>
+        <v>-0.09466942320478725</v>
       </c>
       <c r="AL13" t="n">
         <v>0.9957168698310852</v>
@@ -3079,7 +3079,7 @@
         <v>40.86490387612201</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.30489787649603</v>
+        <v>18.30489787649601</v>
       </c>
       <c r="AO13" t="n">
         <v>0.9992714524269104</v>
@@ -3097,67 +3097,67 @@
         <v>30.29864290927319</v>
       </c>
       <c r="AT13" t="n">
-        <v>24.41943554168051</v>
+        <v>24.41943554168052</v>
       </c>
       <c r="AU13" t="n">
         <v>0.9870516061782837</v>
       </c>
       <c r="AV13" t="n">
+        <v>-0.1004766910634203</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.03342324114860418</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.2558890809404062</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.035548717417619</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.9205452939297274</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.2123051501334956</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.6300358062094809</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.08466497380682902</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.9153406670752986</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.1406902962542578</v>
+      </c>
+      <c r="BF13" t="n">
         <v>112.9591124932053</v>
       </c>
-      <c r="AW13" t="n">
-        <v>103.4425617236773</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>83.33089246089266</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>-0.1004766910634203</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.03342324114860418</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0.2558890809404062</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-0.035548717417619</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0.9205452939297274</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0.2123051501334956</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0.6300358062094809</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0.08466497380682902</v>
-      </c>
       <c r="BG13" t="n">
-        <v>0.9153406670752986</v>
+        <v>103.4425617236772</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.1406902962542578</v>
+        <v>83.33089246089254</v>
       </c>
       <c r="BI13" t="n">
-        <v>-3.077856780921906</v>
+        <v>-3.077856780921955</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-0.3959792934058015</v>
+        <v>-0.3959792934057766</v>
       </c>
       <c r="BK13" t="n">
         <v>-3.625314313251849</v>
       </c>
       <c r="BL13" t="n">
-        <v>-1.660333320037211</v>
+        <v>-1.660333320037147</v>
       </c>
       <c r="BM13" t="n">
         <v>-1.94330320082905</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0.6122456393490587</v>
+        <v>-0.6122456393490054</v>
       </c>
     </row>
     <row r="14">
@@ -3171,7 +3171,7 @@
         <v>134.1718146141539</v>
       </c>
       <c r="D14" t="n">
-        <v>5.121774876371319</v>
+        <v>5.121774876371344</v>
       </c>
       <c r="E14" t="n">
         <v>0.9995135068893433</v>
@@ -3180,7 +3180,7 @@
         <v>116.9079151559383</v>
       </c>
       <c r="G14" t="n">
-        <v>13.85887632978722</v>
+        <v>13.85887632978723</v>
       </c>
       <c r="H14" t="n">
         <v>0.9992885589599609</v>
@@ -3189,7 +3189,7 @@
         <v>101.9287190538772</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.223868512092764</v>
+        <v>-1.223868512092753</v>
       </c>
       <c r="K14" t="n">
         <v>0.9993059635162354</v>
@@ -3198,7 +3198,7 @@
         <v>101.3242924467046</v>
       </c>
       <c r="M14" t="n">
-        <v>4.002494000373986</v>
+        <v>4.002494000374003</v>
       </c>
       <c r="N14" t="n">
         <v>0.9951862692832947</v>
@@ -3207,7 +3207,7 @@
         <v>93.44634198127909</v>
       </c>
       <c r="P14" t="n">
-        <v>12.55166885700629</v>
+        <v>12.55166885700632</v>
       </c>
       <c r="Q14" t="n">
         <v>0.9916736483573914</v>
@@ -3216,7 +3216,7 @@
         <v>102.2135470775848</v>
       </c>
       <c r="S14" t="n">
-        <v>15.99528535883476</v>
+        <v>15.99528535883477</v>
       </c>
       <c r="T14" t="n">
         <v>0.9868114590644836</v>
@@ -3225,7 +3225,7 @@
         <v>99.68034460189496</v>
       </c>
       <c r="V14" t="n">
-        <v>24.89443839864526</v>
+        <v>24.89443839864528</v>
       </c>
       <c r="W14" t="n">
         <v>0.9887672066688538</v>
@@ -3234,7 +3234,7 @@
         <v>59.37266248337766</v>
       </c>
       <c r="Y14" t="n">
-        <v>26.51869591246259</v>
+        <v>26.5186959124626</v>
       </c>
       <c r="Z14" t="n">
         <v>0.9908713698387146</v>
@@ -3243,7 +3243,7 @@
         <v>56.4273347245886</v>
       </c>
       <c r="AB14" t="n">
-        <v>17.24911953540558</v>
+        <v>17.24911953540559</v>
       </c>
       <c r="AC14" t="n">
         <v>0.9733715057373047</v>
@@ -3261,7 +3261,7 @@
         <v>66.60486586550449</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.073639565325806</v>
+        <v>3.073639565325798</v>
       </c>
       <c r="AI14" t="n">
         <v>0.9943244457244873</v>
@@ -3270,7 +3270,7 @@
         <v>74.21466746228806</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.008587127036236097</v>
+        <v>0.008587127036236703</v>
       </c>
       <c r="AL14" t="n">
         <v>0.9964610934257507</v>
@@ -3279,7 +3279,7 @@
         <v>41.55210941395861</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.64224697681183</v>
+        <v>18.64224697681184</v>
       </c>
       <c r="AO14" t="n">
         <v>0.9995734095573425</v>
@@ -3288,7 +3288,7 @@
         <v>30.54434390778237</v>
       </c>
       <c r="AQ14" t="n">
-        <v>23.67909208257149</v>
+        <v>23.67909208257148</v>
       </c>
       <c r="AR14" t="n">
         <v>0.09776253253221512</v>
@@ -3303,61 +3303,61 @@
         <v>0.9790477156639099</v>
       </c>
       <c r="AV14" t="n">
+        <v>-0.003494100367767317</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.1043400865920106</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.1090861381368384</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.1727053459654471</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.020652689832318</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.1031652409979635</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.047939949847283</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.3487597120569124</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.282292223991231</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.342362992306974</v>
+      </c>
+      <c r="BF14" t="n">
         <v>109.2901627611401</v>
       </c>
-      <c r="AW14" t="n">
-        <v>97.30205598382115</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>82.32312663861953</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>-0.003494100367767317</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.1043400865920106</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0.1090861381368384</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-0.1727053459654471</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.020652689832318</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>-0.1031652409979635</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.047939949847283</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0.3487597120569124</v>
-      </c>
       <c r="BG14" t="n">
-        <v>1.282292223991231</v>
+        <v>97.30205598382113</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.342362992306974</v>
+        <v>82.32312663861954</v>
       </c>
       <c r="BI14" t="n">
-        <v>-3.63330152752085</v>
+        <v>-3.633301527520871</v>
       </c>
       <c r="BJ14" t="n">
-        <v>-0.2887568790244117</v>
+        <v>-0.288756879024362</v>
       </c>
       <c r="BK14" t="n">
-        <v>-2.875700564872268</v>
+        <v>-2.875700564872197</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.896315805889362</v>
+        <v>1.896315805889383</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.2087156783496269</v>
+        <v>0.208715678349698</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.175149628383799</v>
+        <v>2.175149628383807</v>
       </c>
     </row>
     <row r="15">
@@ -3380,7 +3380,7 @@
         <v>118.4996990447349</v>
       </c>
       <c r="G15" t="n">
-        <v>13.68612735829456</v>
+        <v>13.68612735829455</v>
       </c>
       <c r="H15" t="n">
         <v>0.9990812540054321</v>
@@ -3398,7 +3398,7 @@
         <v>104.9077460106383</v>
       </c>
       <c r="M15" t="n">
-        <v>4.038141128864709</v>
+        <v>4.038141128864694</v>
       </c>
       <c r="N15" t="n">
         <v>0.9977805018424988</v>
@@ -3407,7 +3407,7 @@
         <v>96.05459659657581</v>
       </c>
       <c r="P15" t="n">
-        <v>10.75652102206615</v>
+        <v>10.75652102206616</v>
       </c>
       <c r="Q15" t="n">
         <v>0.9894351363182068</v>
@@ -3416,7 +3416,7 @@
         <v>104.1579794376455</v>
       </c>
       <c r="S15" t="n">
-        <v>15.46213677588929</v>
+        <v>15.4621367758893</v>
       </c>
       <c r="T15" t="n">
         <v>0.9900572896003723</v>
@@ -3434,7 +3434,7 @@
         <v>61.09783497262509</v>
       </c>
       <c r="Y15" t="n">
-        <v>26.79723374387052</v>
+        <v>26.79723374387051</v>
       </c>
       <c r="Z15" t="n">
         <v>0.9898226261138916</v>
@@ -3443,7 +3443,7 @@
         <v>57.74872962464678</v>
       </c>
       <c r="AB15" t="n">
-        <v>17.67605720682349</v>
+        <v>17.67605720682347</v>
       </c>
       <c r="AC15" t="n">
         <v>0.9799336194992065</v>
@@ -3452,7 +3452,7 @@
         <v>67.82731806978266</v>
       </c>
       <c r="AE15" t="n">
-        <v>15.17989787649603</v>
+        <v>15.17989787649601</v>
       </c>
       <c r="AF15" t="n">
         <v>0.9964691400527954</v>
@@ -3461,7 +3461,7 @@
         <v>66.51679099874293</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.154105328499014</v>
+        <v>3.154105328499003</v>
       </c>
       <c r="AI15" t="n">
         <v>0.9942264556884766</v>
@@ -3470,7 +3470,7 @@
         <v>74.33599106808927</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.008928014877000123</v>
+        <v>0.008928014876994681</v>
       </c>
       <c r="AL15" t="n">
         <v>0.9973823428153992</v>
@@ -3497,67 +3497,67 @@
         <v>29.9667459853152</v>
       </c>
       <c r="AT15" t="n">
-        <v>24.31557026315244</v>
+        <v>24.31557026315243</v>
       </c>
       <c r="AU15" t="n">
         <v>0.9668435454368591</v>
       </c>
       <c r="AV15" t="n">
-        <v>105.6925094381636</v>
+        <v>0.1082034821206008</v>
       </c>
       <c r="AW15" t="n">
+        <v>0.1011604958392169</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.08952161099048794</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.07834637418705981</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.7142148119338003</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.03947197122776558</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.327555230323306</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.1294633175464384</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.600066651689247</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.05804934400193318</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>105.6925094381635</v>
+      </c>
+      <c r="BG15" t="n">
         <v>97.69116059393278</v>
       </c>
-      <c r="AX15" t="n">
-        <v>83.74832381759191</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0.1082034821206008</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0.1011604958392169</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>-0.08952161099048794</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-0.07834637418705981</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0.7142148119338003</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>-0.03947197122776558</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.327555230323306</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0.1294633175464384</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>1.600066651689247</v>
-      </c>
       <c r="BH15" t="n">
-        <v>0.05804934400193318</v>
+        <v>83.74832381759194</v>
       </c>
       <c r="BI15" t="n">
-        <v>-3.655370538970729</v>
+        <v>-3.655370538970679</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0.3490473730707784</v>
+        <v>-0.3490473730707855</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.1673172985268749</v>
+        <v>0.1673172985269176</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.761933751522136</v>
+        <v>0.7619337515220934</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.406996055938549</v>
+        <v>2.406996055938563</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.571073171957561</v>
+        <v>1.571073171957526</v>
       </c>
     </row>
     <row r="16">
@@ -3571,7 +3571,7 @@
         <v>136.8669388142038</v>
       </c>
       <c r="D16" t="n">
-        <v>4.271551903258</v>
+        <v>4.271551903257979</v>
       </c>
       <c r="E16" t="n">
         <v>0.9995972514152527</v>
@@ -3580,7 +3580,7 @@
         <v>119.7885472723778</v>
       </c>
       <c r="G16" t="n">
-        <v>12.48985452854888</v>
+        <v>12.48985452854887</v>
       </c>
       <c r="H16" t="n">
         <v>0.9997735619544983</v>
@@ -3589,7 +3589,7 @@
         <v>111.7958961649144</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5617182305518611</v>
+        <v>-0.5617182305518618</v>
       </c>
       <c r="K16" t="n">
         <v>0.9994493126869202</v>
@@ -3598,7 +3598,7 @@
         <v>107.8389025749044</v>
       </c>
       <c r="M16" t="n">
-        <v>3.250365561627348</v>
+        <v>3.250365561627327</v>
       </c>
       <c r="N16" t="n">
         <v>0.998715877532959</v>
@@ -3607,7 +3607,7 @@
         <v>97.59683811918218</v>
       </c>
       <c r="P16" t="n">
-        <v>9.382889118600417</v>
+        <v>9.382889118600399</v>
       </c>
       <c r="Q16" t="n">
         <v>0.9824255704879761</v>
@@ -3616,7 +3616,7 @@
         <v>105.74113561752</v>
       </c>
       <c r="S16" t="n">
-        <v>14.36603627306351</v>
+        <v>14.3660362730635</v>
       </c>
       <c r="T16" t="n">
         <v>0.9886928796768188</v>
@@ -3643,7 +3643,7 @@
         <v>59.08244518523521</v>
       </c>
       <c r="AB16" t="n">
-        <v>17.89651424326794</v>
+        <v>17.89651424326795</v>
       </c>
       <c r="AC16" t="n">
         <v>0.9647313356399536</v>
@@ -3652,7 +3652,7 @@
         <v>68.60177060391041</v>
       </c>
       <c r="AE16" t="n">
-        <v>14.75024933510639</v>
+        <v>14.75024933510638</v>
       </c>
       <c r="AF16" t="n">
         <v>0.9977972507476807</v>
@@ -3661,7 +3661,7 @@
         <v>66.42582264352352</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.182058131441153</v>
+        <v>3.182058131441157</v>
       </c>
       <c r="AI16" t="n">
         <v>0.9943988919258118</v>
@@ -3670,7 +3670,7 @@
         <v>74.43107442652926</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.1554773208942777</v>
+        <v>-0.1554773208942819</v>
       </c>
       <c r="AL16" t="n">
         <v>0.9979413151741028</v>
@@ -3679,7 +3679,7 @@
         <v>43.3305821520217</v>
       </c>
       <c r="AN16" t="n">
-        <v>20.53586269946808</v>
+        <v>20.53586269946809</v>
       </c>
       <c r="AO16" t="n">
         <v>0.999779999256134</v>
@@ -3703,61 +3703,61 @@
         <v>0.5814077258110046</v>
       </c>
       <c r="AV16" t="n">
+        <v>0.1988268913106666</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.08156959046708323</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.04760661023728119</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.07944614329236899</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.9417087473767864</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.2705462435458585</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.30686658494016</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.02566398458277952</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.398390911995097</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-0.2010802005199697</v>
+      </c>
+      <c r="BF16" t="n">
         <v>101.9794216831987</v>
       </c>
-      <c r="AW16" t="n">
-        <v>97.6366905808749</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>87.13711875049663</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0.1988268913106666</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.08156959046708323</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>-0.04760661023728119</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0.07944614329236899</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0.9417087473767864</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0.2705462435458585</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.30686658494016</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0.02566398458277952</v>
-      </c>
       <c r="BG16" t="n">
-        <v>1.398390911995097</v>
+        <v>97.63669058087497</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.2010802005199697</v>
+        <v>87.13711875049667</v>
       </c>
       <c r="BI16" t="n">
-        <v>-4.331396273662406</v>
+        <v>-4.331396273662442</v>
       </c>
       <c r="BJ16" t="n">
-        <v>-0.988789856272323</v>
+        <v>-0.9887898562723549</v>
       </c>
       <c r="BK16" t="n">
-        <v>-1.351833061827996</v>
+        <v>-1.35183306182801</v>
       </c>
       <c r="BL16" t="n">
-        <v>-1.386289752549754</v>
+        <v>-1.386289752549818</v>
       </c>
       <c r="BM16" t="n">
         <v>3.350862022264749</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.067717428022672</v>
+        <v>1.067717428022625</v>
       </c>
     </row>
     <row r="17">
@@ -3771,7 +3771,7 @@
         <v>138.3303703145778</v>
       </c>
       <c r="D17" t="n">
-        <v>4.715615130485389</v>
+        <v>4.715615130485372</v>
       </c>
       <c r="E17" t="n">
         <v>0.9994179010391235</v>
@@ -3780,7 +3780,7 @@
         <v>121.400086423184</v>
       </c>
       <c r="G17" t="n">
-        <v>13.15351445624171</v>
+        <v>13.15351445624169</v>
       </c>
       <c r="H17" t="n">
         <v>0.9995087385177612</v>
@@ -3789,7 +3789,7 @@
         <v>115.5827542568775</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4571143617021391</v>
+        <v>0.4571143617021277</v>
       </c>
       <c r="K17" t="n">
         <v>0.9992944002151489</v>
@@ -3798,7 +3798,7 @@
         <v>110.62137522596</v>
       </c>
       <c r="M17" t="n">
-        <v>3.079840477476722</v>
+        <v>3.079840477476729</v>
       </c>
       <c r="N17" t="n">
         <v>0.9985561966896057</v>
@@ -3807,7 +3807,7 @@
         <v>99.79284570572224</v>
       </c>
       <c r="P17" t="n">
-        <v>9.638165413065167</v>
+        <v>9.63816541306516</v>
       </c>
       <c r="Q17" t="n">
         <v>0.9870957136154175</v>
@@ -3834,7 +3834,7 @@
         <v>63.89461679661528</v>
       </c>
       <c r="Y17" t="n">
-        <v>27.44009951327709</v>
+        <v>27.4400995132771</v>
       </c>
       <c r="Z17" t="n">
         <v>0.9909409880638123</v>
@@ -3843,7 +3843,7 @@
         <v>60.3624627945271</v>
       </c>
       <c r="AB17" t="n">
-        <v>18.20042386968086</v>
+        <v>18.20042386968085</v>
       </c>
       <c r="AC17" t="n">
         <v>0.9889066219329834</v>
@@ -3852,7 +3852,7 @@
         <v>69.71073556453624</v>
       </c>
       <c r="AE17" t="n">
-        <v>14.54234021775267</v>
+        <v>14.54234021775266</v>
       </c>
       <c r="AF17" t="n">
         <v>0.9960899949073792</v>
@@ -3861,7 +3861,7 @@
         <v>66.42157777826837</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.354823335688167</v>
+        <v>3.354823335688165</v>
       </c>
       <c r="AI17" t="n">
         <v>0.9953151941299438</v>
@@ -3870,7 +3870,7 @@
         <v>74.7336448507106</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.2444003490691671</v>
+        <v>-0.244400349069149</v>
       </c>
       <c r="AL17" t="n">
         <v>0.9979786276817322</v>
@@ -3888,7 +3888,7 @@
         <v>28.8992333919444</v>
       </c>
       <c r="AQ17" t="n">
-        <v>24.67126237585188</v>
+        <v>24.6712623758519</v>
       </c>
       <c r="AR17" t="n">
         <v>0.7446738481521606</v>
@@ -3903,61 +3903,61 @@
         <v>0.09663299471139908</v>
       </c>
       <c r="AV17" t="n">
-        <v>97.02971689083876</v>
+        <v>0.2713426630547673</v>
       </c>
       <c r="AW17" t="n">
-        <v>94.98749447027679</v>
+        <v>0.01774442956802957</v>
       </c>
       <c r="AX17" t="n">
-        <v>90.45004786212141</v>
+        <v>0.06937067559425003</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.2713426630547673</v>
+        <v>0.1668747435224809</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.01774442956802957</v>
+        <v>1.255307299025517</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.06937067559425003</v>
+        <v>0.1050695459893412</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.1668747435224809</v>
+        <v>1.378883199488865</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.255307299025517</v>
+        <v>0.04112061033857728</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.1050695459893412</v>
+        <v>1.197906250649307</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.378883199488865</v>
+        <v>-0.07542143476770313</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.04112061033857728</v>
+        <v>97.02971689083864</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.197906250649307</v>
+        <v>94.98749447027676</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.07542143476770313</v>
+        <v>90.45004786212144</v>
       </c>
       <c r="BI17" t="n">
-        <v>-5.632950251515375</v>
+        <v>-5.632950251515389</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.3843534279117264</v>
+        <v>0.3843534279117939</v>
       </c>
       <c r="BK17" t="n">
-        <v>-2.605262206572633</v>
+        <v>-2.605262206572718</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0.2753742289137762</v>
+        <v>-0.275374228913762</v>
       </c>
       <c r="BM17" t="n">
-        <v>4.542430911983892</v>
+        <v>4.542430911983814</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.1385353394288451</v>
+        <v>0.138535339428838</v>
       </c>
     </row>
     <row r="18">
@@ -3971,7 +3971,7 @@
         <v>139.3823826566656</v>
       </c>
       <c r="D18" t="n">
-        <v>4.961979642827458</v>
+        <v>4.96197964282746</v>
       </c>
       <c r="E18" t="n">
         <v>0.9988729357719421</v>
@@ -3980,7 +3980,7 @@
         <v>122.9394060500125</v>
       </c>
       <c r="G18" t="n">
-        <v>13.22268222240692</v>
+        <v>13.22268222240691</v>
       </c>
       <c r="H18" t="n">
         <v>0.999428927898407</v>
@@ -3989,7 +3989,7 @@
         <v>119.4352900728266</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6793245356133752</v>
+        <v>0.6793245356133644</v>
       </c>
       <c r="K18" t="n">
         <v>0.9988402724266052</v>
@@ -3998,7 +3998,7 @@
         <v>114.5848456849443</v>
       </c>
       <c r="M18" t="n">
-        <v>3.027765801612361</v>
+        <v>3.027765801612367</v>
       </c>
       <c r="N18" t="n">
         <v>0.9974349141120911</v>
@@ -4007,7 +4007,7 @@
         <v>102.6977295571185</v>
       </c>
       <c r="P18" t="n">
-        <v>9.777052859042556</v>
+        <v>9.777052859042554</v>
       </c>
       <c r="Q18" t="n">
         <v>0.9803855419158936</v>
@@ -4025,7 +4025,7 @@
         <v>107.5965313201255</v>
       </c>
       <c r="V18" t="n">
-        <v>22.85057230198638</v>
+        <v>22.85057230198637</v>
       </c>
       <c r="W18" t="n">
         <v>0.9908298254013062</v>
@@ -4034,7 +4034,7 @@
         <v>64.96860828805477</v>
       </c>
       <c r="Y18" t="n">
-        <v>27.01200119992521</v>
+        <v>27.0120011999252</v>
       </c>
       <c r="Z18" t="n">
         <v>0.9890455007553101</v>
@@ -4043,7 +4043,7 @@
         <v>61.84021158421294</v>
       </c>
       <c r="AB18" t="n">
-        <v>18.16282881067156</v>
+        <v>18.16282881067155</v>
       </c>
       <c r="AC18" t="n">
         <v>0.9897379279136658</v>
@@ -4052,7 +4052,7 @@
         <v>71.11238520196144</v>
       </c>
       <c r="AE18" t="n">
-        <v>13.70208415579287</v>
+        <v>13.70208415579289</v>
       </c>
       <c r="AF18" t="n">
         <v>0.9940496683120728</v>
@@ -4061,7 +4061,7 @@
         <v>66.56456399471202</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.124659112159236</v>
+        <v>3.124659112159242</v>
       </c>
       <c r="AI18" t="n">
         <v>0.9959275126457214</v>
@@ -4070,7 +4070,7 @@
         <v>74.9737597526388</v>
       </c>
       <c r="AK18" t="n">
-        <v>-0.6156759059175556</v>
+        <v>-0.6156759059175533</v>
       </c>
       <c r="AL18" t="n">
         <v>0.9980252981185913</v>
@@ -4079,7 +4079,7 @@
         <v>45.9621104788273</v>
       </c>
       <c r="AN18" t="n">
-        <v>21.57527842420214</v>
+        <v>21.57527842420213</v>
       </c>
       <c r="AO18" t="n">
         <v>0.9995974898338318</v>
@@ -4097,72 +4097,72 @@
         <v>23.67486142097636</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.987718947390306</v>
+        <v>8.987718947390293</v>
       </c>
       <c r="AU18" t="n">
         <v>0.02904342673718929</v>
       </c>
       <c r="AV18" t="n">
-        <v>90.71352118016793</v>
+        <v>0.2343157504467257</v>
       </c>
       <c r="AW18" t="n">
-        <v>92.42616616772963</v>
+        <v>-0.04769386129176212</v>
       </c>
       <c r="AX18" t="n">
-        <v>96.22198057446441</v>
+        <v>0.2861428768076806</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.2343157504467257</v>
+        <v>0.0746067534101762</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0.04769386129176212</v>
+        <v>1.151847839355469</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.2861428768076806</v>
+        <v>-0.1881518262497934</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.0746067534101762</v>
+        <v>1.389107805617314</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.151847839355469</v>
+        <v>-0.1584600895009149</v>
       </c>
       <c r="BD18" t="n">
-        <v>-0.1881518262497934</v>
+        <v>1.247548042459691</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.389107805617314</v>
+        <v>-0.003818755454203071</v>
       </c>
       <c r="BF18" t="n">
-        <v>-0.1584600895009149</v>
+        <v>90.71352118016796</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.247548042459691</v>
+        <v>92.42616616772953</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.003818755454203071</v>
+        <v>96.2219805744643</v>
       </c>
       <c r="BI18" t="n">
-        <v>-3.562689417838953</v>
+        <v>-3.562689417838854</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1.367173211738923</v>
+        <v>1.367173211738915</v>
       </c>
       <c r="BK18" t="n">
-        <v>-1.902581519655548</v>
+        <v>-1.902581519655534</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.8537475787637199</v>
+        <v>0.8537475787637732</v>
       </c>
       <c r="BM18" t="n">
-        <v>3.62793270112244</v>
+        <v>3.627932701122425</v>
       </c>
       <c r="BN18" t="n">
-        <v>-1.235048825257806</v>
+        <v>-1.235048825257763</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5.35</v>
+        <v>5.350000000000001</v>
       </c>
       <c r="B19" t="b">
         <v>0</v>
@@ -4171,7 +4171,7 @@
         <v>140.6396419443983</v>
       </c>
       <c r="D19" t="n">
-        <v>5.759673422955444</v>
+        <v>5.759673422955452</v>
       </c>
       <c r="E19" t="n">
         <v>0.9996495246887207</v>
@@ -4180,7 +4180,7 @@
         <v>124.2064212230926</v>
       </c>
       <c r="G19" t="n">
-        <v>13.7372443016539</v>
+        <v>13.73724430165392</v>
       </c>
       <c r="H19" t="n">
         <v>0.9998618364334106</v>
@@ -4189,7 +4189,7 @@
         <v>121.7171445805976</v>
       </c>
       <c r="J19" t="n">
-        <v>1.076913387217417</v>
+        <v>1.07691338721742</v>
       </c>
       <c r="K19" t="n">
         <v>0.9965078234672546</v>
@@ -4198,7 +4198,7 @@
         <v>116.6416087049119</v>
       </c>
       <c r="M19" t="n">
-        <v>2.934914446891611</v>
+        <v>2.934914446891622</v>
       </c>
       <c r="N19" t="n">
         <v>0.9985040426254272</v>
@@ -4207,7 +4207,7 @@
         <v>105.4180307591215</v>
       </c>
       <c r="P19" t="n">
-        <v>9.185677386344736</v>
+        <v>9.185677386344748</v>
       </c>
       <c r="Q19" t="n">
         <v>0.9792495369911194</v>
@@ -4216,7 +4216,7 @@
         <v>112.3424773520612</v>
       </c>
       <c r="S19" t="n">
-        <v>14.72525089345078</v>
+        <v>14.7252508934508</v>
       </c>
       <c r="T19" t="n">
         <v>0.992723286151886</v>
@@ -4225,7 +4225,7 @@
         <v>109.4055906255195</v>
       </c>
       <c r="V19" t="n">
-        <v>23.31890349692486</v>
+        <v>23.31890349692487</v>
       </c>
       <c r="W19" t="n">
         <v>0.9862653613090515</v>
@@ -4234,7 +4234,7 @@
         <v>66.38971288153466</v>
       </c>
       <c r="Y19" t="n">
-        <v>27.48521033753741</v>
+        <v>27.4852103375374</v>
       </c>
       <c r="Z19" t="n">
         <v>0.9891728162765503</v>
@@ -4243,7 +4243,7 @@
         <v>63.14067840576173</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.19566767266457</v>
+        <v>18.19566767266456</v>
       </c>
       <c r="AC19" t="n">
         <v>0.9891736507415771</v>
@@ -4252,7 +4252,7 @@
         <v>72.01443124324717</v>
       </c>
       <c r="AE19" t="n">
-        <v>13.677523998504</v>
+        <v>13.67752399850399</v>
       </c>
       <c r="AF19" t="n">
         <v>0.9974967837333679</v>
@@ -4261,7 +4261,7 @@
         <v>66.99386353188373</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.292424628075139</v>
+        <v>3.292424628075133</v>
       </c>
       <c r="AI19" t="n">
         <v>0.9969262480735779</v>
@@ -4270,7 +4270,7 @@
         <v>75.20227635160406</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.6589524289394717</v>
+        <v>-0.6589524289394947</v>
       </c>
       <c r="AL19" t="n">
         <v>0.9981861710548401</v>
@@ -4288,7 +4288,7 @@
         <v>29.27224179531666</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24.6021757734583</v>
+        <v>24.60217577345828</v>
       </c>
       <c r="AR19" t="n">
         <v>0.9334888458251953</v>
@@ -4297,67 +4297,67 @@
         <v>23.48921958436357</v>
       </c>
       <c r="AT19" t="n">
-        <v>14.0703728858461</v>
+        <v>14.07037288584608</v>
       </c>
       <c r="AU19" t="n">
         <v>0.1820123940706253</v>
       </c>
       <c r="AV19" t="n">
-        <v>89.90433805516085</v>
+        <v>0.175954940471243</v>
       </c>
       <c r="AW19" t="n">
+        <v>-0.1097861756669687</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.2185841824146024</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.1939499631841137</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.8790036465259305</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-0.04239995428856247</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.061963020487035</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.07732573975908075</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.190268739740901</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.005960464477539062</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>89.90433805516093</v>
+      </c>
+      <c r="BG19" t="n">
         <v>91.18233143096569</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BH19" t="n">
         <v>97.70591326436629</v>
       </c>
-      <c r="AY19" t="n">
-        <v>0.175954940471243</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>-0.1097861756669687</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0.2185841824146024</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>-0.1939499631841137</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0.8790036465259305</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>-0.04239995428856247</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.061963020487035</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>-0.07732573975908075</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.190268739740901</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>0.005960464477539062</v>
-      </c>
       <c r="BI19" t="n">
-        <v>-2.89860382803753</v>
+        <v>-2.898603828037558</v>
       </c>
       <c r="BJ19" t="n">
-        <v>-1.247044024999681</v>
+        <v>-1.247044024999742</v>
       </c>
       <c r="BK19" t="n">
-        <v>-0.8977670490451928</v>
+        <v>-0.8977670490451715</v>
       </c>
       <c r="BL19" t="n">
-        <v>-0.282528382326884</v>
+        <v>-0.2825283823269054</v>
       </c>
       <c r="BM19" t="n">
-        <v>2.07233326146828</v>
+        <v>2.072333261468287</v>
       </c>
       <c r="BN19" t="n">
-        <v>-0.04710188781277935</v>
+        <v>-0.04710188781277225</v>
       </c>
     </row>
     <row r="20">
@@ -4371,7 +4371,7 @@
         <v>142.0896651897025</v>
       </c>
       <c r="D20" t="n">
-        <v>4.60248906561668</v>
+        <v>4.602489065616689</v>
       </c>
       <c r="E20" t="n">
         <v>0.9996440410614014</v>
@@ -4380,7 +4380,7 @@
         <v>125.8225785925033</v>
       </c>
       <c r="G20" t="n">
-        <v>13.32652315180351</v>
+        <v>13.32652315180352</v>
       </c>
       <c r="H20" t="n">
         <v>0.9996563196182251</v>
@@ -4389,7 +4389,7 @@
         <v>124.0885876594706</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8379997091090274</v>
+        <v>0.8379997091090426</v>
       </c>
       <c r="K20" t="n">
         <v>0.9990775585174561</v>
@@ -4398,7 +4398,7 @@
         <v>118.8546201016041</v>
       </c>
       <c r="M20" t="n">
-        <v>2.616914789727389</v>
+        <v>2.616914789727394</v>
       </c>
       <c r="N20" t="n">
         <v>0.9969648718833923</v>
@@ -4407,7 +4407,7 @@
         <v>106.8400606195978</v>
       </c>
       <c r="P20" t="n">
-        <v>8.756564525847722</v>
+        <v>8.75656452584774</v>
       </c>
       <c r="Q20" t="n">
         <v>0.98325115442276</v>
@@ -4434,7 +4434,7 @@
         <v>67.34914576753657</v>
       </c>
       <c r="Y20" t="n">
-        <v>28.0387634926654</v>
+        <v>28.03876349266539</v>
       </c>
       <c r="Z20" t="n">
         <v>0.9825542569160461</v>
@@ -4452,7 +4452,7 @@
         <v>72.87039249501331</v>
       </c>
       <c r="AE20" t="n">
-        <v>13.70456776720411</v>
+        <v>13.70456776720412</v>
       </c>
       <c r="AF20" t="n">
         <v>0.997517466545105</v>
@@ -4461,7 +4461,7 @@
         <v>67.00173235954122</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.70004532185007</v>
+        <v>3.700045321850067</v>
       </c>
       <c r="AI20" t="n">
         <v>0.9963506460189819</v>
@@ -4470,7 +4470,7 @@
         <v>75.32566963358128</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.2368358855551946</v>
+        <v>-0.2368358855551862</v>
       </c>
       <c r="AL20" t="n">
         <v>0.99803227186203</v>
@@ -4488,7 +4488,7 @@
         <v>30.23416235091839</v>
       </c>
       <c r="AQ20" t="n">
-        <v>24.09296238676032</v>
+        <v>24.09296238676031</v>
       </c>
       <c r="AR20" t="n">
         <v>0.9146105051040649</v>
@@ -4497,67 +4497,67 @@
         <v>23.13378719573326</v>
       </c>
       <c r="AT20" t="n">
-        <v>13.812710376496</v>
+        <v>13.81271037649601</v>
       </c>
       <c r="AU20" t="n">
         <v>0.1864916831254959</v>
       </c>
       <c r="AV20" t="n">
-        <v>84.91631352409287</v>
+        <v>0.01474339911278832</v>
       </c>
       <c r="AW20" t="n">
-        <v>90.63063206963925</v>
+        <v>-0.07048870654816142</v>
       </c>
       <c r="AX20" t="n">
-        <v>100.366647097401</v>
+        <v>-0.1017570495605469</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.01474339911278832</v>
+        <v>-0.1052420190040095</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-0.07048870654816142</v>
+        <v>1.067047930778344</v>
       </c>
       <c r="BA20" t="n">
-        <v>-0.1017570495605469</v>
+        <v>0.03111819003490623</v>
       </c>
       <c r="BB20" t="n">
-        <v>-0.1052420190040095</v>
+        <v>1.234456326099153</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.067047930778344</v>
+        <v>0.2039107870548307</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.03111819003490623</v>
+        <v>1.259468971414769</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.234456326099153</v>
+        <v>0.1166678489522717</v>
       </c>
       <c r="BF20" t="n">
-        <v>0.2039107870548307</v>
+        <v>84.91631352409284</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.259468971414769</v>
+        <v>90.63063206963919</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.1166678489522717</v>
+        <v>100.3666470974009</v>
       </c>
       <c r="BI20" t="n">
-        <v>-6.056777467838316</v>
+        <v>-6.056777467838337</v>
       </c>
       <c r="BJ20" t="n">
-        <v>-0.8194482428653949</v>
+        <v>-0.8194482428653629</v>
       </c>
       <c r="BK20" t="n">
-        <v>-2.467638284309317</v>
+        <v>-2.467638284309345</v>
       </c>
       <c r="BL20" t="n">
-        <v>-0.3101960274642686</v>
+        <v>-0.3101960274642721</v>
       </c>
       <c r="BM20" t="n">
         <v>3.533728925496881</v>
       </c>
       <c r="BN20" t="n">
-        <v>0.944417751816065</v>
+        <v>0.9444177518160792</v>
       </c>
     </row>
     <row r="21">
@@ -4571,7 +4571,7 @@
         <v>142.5730603806516</v>
       </c>
       <c r="D21" t="n">
-        <v>4.124953898977736</v>
+        <v>4.124953898977727</v>
       </c>
       <c r="E21" t="n">
         <v>0.9995334148406982</v>
@@ -4589,7 +4589,7 @@
         <v>126.0611676155253</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6868240681100417</v>
+        <v>0.6868240681100399</v>
       </c>
       <c r="K21" t="n">
         <v>0.9967188239097595</v>
@@ -4598,7 +4598,7 @@
         <v>120.7761967435796</v>
       </c>
       <c r="M21" t="n">
-        <v>2.512197291597431</v>
+        <v>2.512197291597407</v>
       </c>
       <c r="N21" t="n">
         <v>0.9985330104827881</v>
@@ -4607,7 +4607,7 @@
         <v>109.4484856788148</v>
       </c>
       <c r="P21" t="n">
-        <v>8.289369623711792</v>
+        <v>8.289369623711769</v>
       </c>
       <c r="Q21" t="n">
         <v>0.9859683513641357</v>
@@ -4616,7 +4616,7 @@
         <v>116.4911473051031</v>
       </c>
       <c r="S21" t="n">
-        <v>13.91931087412735</v>
+        <v>13.91931087412733</v>
       </c>
       <c r="T21" t="n">
         <v>0.9956381916999817</v>
@@ -4625,7 +4625,7 @@
         <v>113.041045817923</v>
       </c>
       <c r="V21" t="n">
-        <v>22.42290415662401</v>
+        <v>22.422904156624</v>
       </c>
       <c r="W21" t="n">
         <v>0.9873035550117493</v>
@@ -4634,7 +4634,7 @@
         <v>68.9086508243642</v>
       </c>
       <c r="Y21" t="n">
-        <v>28.80728701327709</v>
+        <v>28.8072870132771</v>
       </c>
       <c r="Z21" t="n">
         <v>0.9854573607444763</v>
@@ -4643,7 +4643,7 @@
         <v>65.60959105796003</v>
       </c>
       <c r="AB21" t="n">
-        <v>19.72031288958613</v>
+        <v>19.7203128895861</v>
       </c>
       <c r="AC21" t="n">
         <v>0.987862229347229</v>
@@ -4661,7 +4661,7 @@
         <v>66.79034943276264</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.544570598196486</v>
+        <v>4.544570598196477</v>
       </c>
       <c r="AI21" t="n">
         <v>0.9972565770149231</v>
@@ -4670,7 +4670,7 @@
         <v>75.23176314982963</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.3779309861203615</v>
+        <v>0.3779309861203458</v>
       </c>
       <c r="AL21" t="n">
         <v>0.9980725049972534</v>
@@ -4679,7 +4679,7 @@
         <v>50.04987107946518</v>
       </c>
       <c r="AN21" t="n">
-        <v>23.75384391622342</v>
+        <v>23.75384391622341</v>
       </c>
       <c r="AO21" t="n">
         <v>0.999737560749054</v>
@@ -4697,67 +4697,67 @@
         <v>22.01653541402614</v>
       </c>
       <c r="AT21" t="n">
-        <v>12.28384464345081</v>
+        <v>12.2838446434508</v>
       </c>
       <c r="AU21" t="n">
         <v>0.2039229720830917</v>
       </c>
       <c r="AV21" t="n">
-        <v>77.79078311948422</v>
+        <v>0.03497752737492021</v>
       </c>
       <c r="AW21" t="n">
-        <v>86.24705486234706</v>
+        <v>0.08218237694273256</v>
       </c>
       <c r="AX21" t="n">
+        <v>0.008100144406583354</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.2697041694154123</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.941240026595743</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-0.145341994914606</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.469784594596696</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-0.0834424444969688</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.423604437645444</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>-0.06741158505703737</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>77.79078311948426</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>86.247054862347</v>
+      </c>
+      <c r="BH21" t="n">
         <v>104.77337111536</v>
       </c>
-      <c r="AY21" t="n">
-        <v>0.03497752737492021</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0.08218237694273256</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0.008100144406583354</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0.2697041694154123</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0.941240026595743</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>-0.145341994914606</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.469784594596696</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>-0.0834424444969688</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>1.423604437645444</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>-0.06741158505703737</v>
-      </c>
       <c r="BI21" t="n">
-        <v>-4.537500313768319</v>
+        <v>-4.537500313768284</v>
       </c>
       <c r="BJ21" t="n">
         <v>2.146953741077088</v>
       </c>
       <c r="BK21" t="n">
-        <v>-1.51815910397373</v>
+        <v>-1.518159103973716</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.9430745195161272</v>
+        <v>0.9430745195161592</v>
       </c>
       <c r="BM21" t="n">
-        <v>3.96116876510041</v>
+        <v>3.961168765100446</v>
       </c>
       <c r="BN21" t="n">
-        <v>-1.342422375744057</v>
+        <v>-1.342422375744036</v>
       </c>
     </row>
     <row r="22">
@@ -4771,7 +4771,7 @@
         <v>144.0718792854472</v>
       </c>
       <c r="D22" t="n">
-        <v>4.883591672207444</v>
+        <v>4.883591672207447</v>
       </c>
       <c r="E22" t="n">
         <v>0.9991480112075806</v>
@@ -4780,7 +4780,7 @@
         <v>127.9098591905959</v>
       </c>
       <c r="G22" t="n">
-        <v>13.42057573034407</v>
+        <v>13.42057573034408</v>
       </c>
       <c r="H22" t="n">
         <v>0.999875545501709</v>
@@ -4789,7 +4789,7 @@
         <v>128.7167488260472</v>
       </c>
       <c r="J22" t="n">
-        <v>1.433644396193472</v>
+        <v>1.433644396193484</v>
       </c>
       <c r="K22" t="n">
         <v>0.9990392923355103</v>
@@ -4798,7 +4798,7 @@
         <v>123.0473457498753</v>
       </c>
       <c r="M22" t="n">
-        <v>2.898293353141611</v>
+        <v>2.898293353141622</v>
       </c>
       <c r="N22" t="n">
         <v>0.9972526431083679</v>
@@ -4807,7 +4807,7 @@
         <v>111.0186231897232</v>
       </c>
       <c r="P22" t="n">
-        <v>8.901604185713097</v>
+        <v>8.901604185713099</v>
       </c>
       <c r="Q22" t="n">
         <v>0.9862622022628784</v>
@@ -4816,7 +4816,7 @@
         <v>117.9734980806391</v>
       </c>
       <c r="S22" t="n">
-        <v>14.33796984084108</v>
+        <v>14.33796984084109</v>
       </c>
       <c r="T22" t="n">
         <v>0.9911631345748901</v>
@@ -4825,7 +4825,7 @@
         <v>114.64071882532</v>
       </c>
       <c r="V22" t="n">
-        <v>22.44744808115857</v>
+        <v>22.44744808115858</v>
       </c>
       <c r="W22" t="n">
         <v>0.9849469661712646</v>
@@ -4834,7 +4834,7 @@
         <v>70.19635464282746</v>
       </c>
       <c r="Y22" t="n">
-        <v>28.4227898780336</v>
+        <v>28.42278987803358</v>
       </c>
       <c r="Z22" t="n">
         <v>0.9832934141159058</v>
@@ -4843,7 +4843,7 @@
         <v>66.9037068143804</v>
       </c>
       <c r="AB22" t="n">
-        <v>19.51646196081285</v>
+        <v>19.51646196081283</v>
       </c>
       <c r="AC22" t="n">
         <v>0.989772617816925</v>
@@ -4852,7 +4852,7 @@
         <v>74.75287254820479</v>
       </c>
       <c r="AE22" t="n">
-        <v>13.25543992062833</v>
+        <v>13.25543992062832</v>
       </c>
       <c r="AF22" t="n">
         <v>0.9934626817703247</v>
@@ -4861,7 +4861,7 @@
         <v>67.01793264835439</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.352358554271945</v>
+        <v>4.352358554271942</v>
       </c>
       <c r="AI22" t="n">
         <v>0.9970760345458984</v>
@@ -4870,7 +4870,7 @@
         <v>75.39562468833113</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.1158531675947643</v>
+        <v>0.1158531675947473</v>
       </c>
       <c r="AL22" t="n">
         <v>0.9979460835456848</v>
@@ -4879,7 +4879,7 @@
         <v>51.32940576431599</v>
       </c>
       <c r="AN22" t="n">
-        <v>23.46558266497675</v>
+        <v>23.46558266497673</v>
       </c>
       <c r="AO22" t="n">
         <v>0.9999175071716309</v>
@@ -4888,7 +4888,7 @@
         <v>32.25564347936752</v>
       </c>
       <c r="AQ22" t="n">
-        <v>22.51044740068153</v>
+        <v>22.51044740068152</v>
       </c>
       <c r="AR22" t="n">
         <v>0.8166743516921997</v>
@@ -4897,67 +4897,67 @@
         <v>21.91640772718064</v>
       </c>
       <c r="AT22" t="n">
-        <v>11.16818367166724</v>
+        <v>11.16818367166722</v>
       </c>
       <c r="AU22" t="n">
         <v>0.5830644965171814</v>
       </c>
       <c r="AV22" t="n">
-        <v>75.84131289655623</v>
+        <v>0.1791081529982534</v>
       </c>
       <c r="AW22" t="n">
-        <v>87.59431386169179</v>
+        <v>0.08635825299201727</v>
       </c>
       <c r="AX22" t="n">
+        <v>0.4376512892702777</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.05912172033431773</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.7763639409491319</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>-0.2084407400577604</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.067571437105215</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>-0.4150735571029287</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.124645801300694</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>-0.2920515993808159</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>75.84131289655627</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>87.59431386169176</v>
+      </c>
+      <c r="BH22" t="n">
         <v>108.2889846276018</v>
       </c>
-      <c r="AY22" t="n">
-        <v>0.1791081529982534</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0.08635825299201727</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0.4376512892702777</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0.05912172033431773</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0.7763639409491319</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>-0.2084407400577604</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.067571437105215</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>-0.4150735571029287</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>1.124645801300694</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>-0.2920515993808159</v>
-      </c>
       <c r="BI22" t="n">
-        <v>-1.762869985684141</v>
+        <v>-1.762869985684162</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1.484094119014859</v>
+        <v>1.484094119014852</v>
       </c>
       <c r="BK22" t="n">
-        <v>-0.5814892452770621</v>
+        <v>-0.5814892452770266</v>
       </c>
       <c r="BL22" t="n">
-        <v>-0.1089624803039477</v>
+        <v>-0.1089624803039442</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.8488841740087665</v>
+        <v>0.8488841740088091</v>
       </c>
       <c r="BN22" t="n">
-        <v>-2.375280364838364</v>
+        <v>-2.375280364838389</v>
       </c>
     </row>
     <row r="23">
@@ -4971,7 +4971,7 @@
         <v>145.1342968230552</v>
       </c>
       <c r="D23" t="n">
-        <v>5.263697847406888</v>
+        <v>5.263697847406915</v>
       </c>
       <c r="E23" t="n">
         <v>0.9997550845146179</v>
@@ -4989,7 +4989,7 @@
         <v>130.8524436139046</v>
       </c>
       <c r="J23" t="n">
-        <v>1.704569065824444</v>
+        <v>1.704569065824468</v>
       </c>
       <c r="K23" t="n">
         <v>0.996533989906311</v>
@@ -4998,7 +4998,7 @@
         <v>125.3825005064619</v>
       </c>
       <c r="M23" t="n">
-        <v>3.170289384557833</v>
+        <v>3.170289384557846</v>
       </c>
       <c r="N23" t="n">
         <v>0.9972280859947205</v>
@@ -5007,7 +5007,7 @@
         <v>112.707974048371</v>
       </c>
       <c r="P23" t="n">
-        <v>8.402219731756958</v>
+        <v>8.402219731756983</v>
       </c>
       <c r="Q23" t="n">
         <v>0.9792482852935791</v>
@@ -5025,7 +5025,7 @@
         <v>115.9122385877244</v>
       </c>
       <c r="V23" t="n">
-        <v>22.37410849713262</v>
+        <v>22.37410849713265</v>
       </c>
       <c r="W23" t="n">
         <v>0.9898754954338074</v>
@@ -5034,7 +5034,7 @@
         <v>71.15794242696559</v>
       </c>
       <c r="Y23" t="n">
-        <v>28.17037054832946</v>
+        <v>28.17037054832945</v>
       </c>
       <c r="Z23" t="n">
         <v>0.993791401386261</v>
@@ -5043,7 +5043,7 @@
         <v>67.74473393217046</v>
       </c>
       <c r="AB23" t="n">
-        <v>19.16526632106053</v>
+        <v>19.16526632106051</v>
       </c>
       <c r="AC23" t="n">
         <v>0.9910605549812317</v>
@@ -5052,7 +5052,7 @@
         <v>75.70125498670212</v>
       </c>
       <c r="AE23" t="n">
-        <v>13.11950683593753</v>
+        <v>13.1195068359375</v>
       </c>
       <c r="AF23" t="n">
         <v>0.9830417633056641</v>
@@ -5061,7 +5061,7 @@
         <v>67.66565201130319</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.240449945977417</v>
+        <v>4.240449945977394</v>
       </c>
       <c r="AI23" t="n">
         <v>0.9857773184776306</v>
@@ -5070,7 +5070,7 @@
         <v>75.58997945582614</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.3049972209524867</v>
+        <v>0.3049972209524601</v>
       </c>
       <c r="AL23" t="n">
         <v>0.9977414608001709</v>
@@ -5079,7 +5079,7 @@
         <v>52.46590147627161</v>
       </c>
       <c r="AN23" t="n">
-        <v>23.00307902883978</v>
+        <v>23.00307902883976</v>
       </c>
       <c r="AO23" t="n">
         <v>0.9998509883880615</v>
@@ -5088,7 +5088,7 @@
         <v>32.84003480951837</v>
       </c>
       <c r="AQ23" t="n">
-        <v>21.60386430456285</v>
+        <v>21.60386430456283</v>
       </c>
       <c r="AR23" t="n">
         <v>0.8735920190811157</v>
@@ -5097,67 +5097,67 @@
         <v>21.60928807360061</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.638308910613375</v>
+        <v>8.638308910613365</v>
       </c>
       <c r="AU23" t="n">
         <v>0.5651276707649231</v>
       </c>
       <c r="AV23" t="n">
+        <v>0.2076940333589548</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.840732006248459e-05</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.1263435850752188</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>-0.2144478737039748</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.5243585464802223</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>-0.2100132881326857</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0.6396374803908387</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>-0.1525787597006918</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0.8395012388838126</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>-0.1680739382480034</v>
+      </c>
+      <c r="BF23" t="n">
         <v>74.26504314811594</v>
       </c>
-      <c r="AW23" t="n">
-        <v>85.08407637179293</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>106.4711394633776</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0.2076940333589548</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>2.840732006248459e-05</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0.1263435850752188</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>-0.2144478737039748</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0.5243585464802223</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>-0.2100132881326857</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0.6396374803908387</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>-0.1525787597006918</v>
-      </c>
       <c r="BG23" t="n">
-        <v>0.8395012388838126</v>
+        <v>85.08407637179295</v>
       </c>
       <c r="BH23" t="n">
-        <v>-0.1680739382480034</v>
+        <v>106.4711394633777</v>
       </c>
       <c r="BI23" t="n">
-        <v>-1.569312075738601</v>
+        <v>-1.56931207573858</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.1991170428661988</v>
+        <v>0.1991170428662095</v>
       </c>
       <c r="BK23" t="n">
-        <v>-1.736084064581625</v>
+        <v>-1.736084064581604</v>
       </c>
       <c r="BL23" t="n">
-        <v>-0.3370539000059551</v>
+        <v>-0.3370539000059871</v>
       </c>
       <c r="BM23" t="n">
-        <v>-0.7893919645763177</v>
+        <v>-0.7893919645763319</v>
       </c>
       <c r="BN23" t="n">
-        <v>-0.3234350967777395</v>
+        <v>-0.323435096777775</v>
       </c>
     </row>
     <row r="24">
@@ -5171,7 +5171,7 @@
         <v>146.5402319076213</v>
       </c>
       <c r="D24" t="n">
-        <v>5.326112787774264</v>
+        <v>5.326112787774269</v>
       </c>
       <c r="E24" t="n">
         <v>0.9997219443321228</v>
@@ -5180,7 +5180,7 @@
         <v>130.2357125789561</v>
       </c>
       <c r="G24" t="n">
-        <v>13.91672986619017</v>
+        <v>13.91672986619016</v>
       </c>
       <c r="H24" t="n">
         <v>0.9997363686561584</v>
@@ -5189,7 +5189,7 @@
         <v>133.0626386277219</v>
       </c>
       <c r="J24" t="n">
-        <v>2.016627534906917</v>
+        <v>2.016627534906915</v>
       </c>
       <c r="K24" t="n">
         <v>0.9978614449501038</v>
@@ -5198,7 +5198,7 @@
         <v>128.1267693702211</v>
       </c>
       <c r="M24" t="n">
-        <v>2.778998841630653</v>
+        <v>2.778998841630652</v>
       </c>
       <c r="N24" t="n">
         <v>0.9951602816581726</v>
@@ -5207,7 +5207,7 @@
         <v>114.6529826712101</v>
       </c>
       <c r="P24" t="n">
-        <v>8.17129256877493</v>
+        <v>8.171292568774934</v>
       </c>
       <c r="Q24" t="n">
         <v>0.9803906679153442</v>
@@ -5216,7 +5216,7 @@
         <v>121.0138523832281</v>
       </c>
       <c r="S24" t="n">
-        <v>13.97959932367851</v>
+        <v>13.97959932367852</v>
       </c>
       <c r="T24" t="n">
         <v>0.9960368275642395</v>
@@ -5225,7 +5225,7 @@
         <v>117.5420964017828</v>
       </c>
       <c r="V24" t="n">
-        <v>22.41946281270776</v>
+        <v>22.41946281270778</v>
       </c>
       <c r="W24" t="n">
         <v>0.9850353002548218</v>
@@ -5243,7 +5243,7 @@
         <v>68.18298177516208</v>
       </c>
       <c r="AB24" t="n">
-        <v>19.30363431889958</v>
+        <v>19.3036343188996</v>
       </c>
       <c r="AC24" t="n">
         <v>0.9933276176452637</v>
@@ -5252,7 +5252,7 @@
         <v>75.80158964116524</v>
       </c>
       <c r="AE24" t="n">
-        <v>12.91213339947637</v>
+        <v>12.9121333994764</v>
       </c>
       <c r="AF24" t="n">
         <v>0.9793947339057922</v>
@@ -5261,7 +5261,7 @@
         <v>67.27061981850483</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.637032366813486</v>
+        <v>4.637032366813497</v>
       </c>
       <c r="AI24" t="n">
         <v>0.9962270259857178</v>
@@ -5279,7 +5279,7 @@
         <v>53.64847386136968</v>
       </c>
       <c r="AN24" t="n">
-        <v>22.53443941156914</v>
+        <v>22.53443941156915</v>
       </c>
       <c r="AO24" t="n">
         <v>0.9986785054206848</v>
@@ -5288,7 +5288,7 @@
         <v>32.24390313980427</v>
       </c>
       <c r="AQ24" t="n">
-        <v>20.25479255838596</v>
+        <v>20.25479255838597</v>
       </c>
       <c r="AR24" t="n">
         <v>0.9116175174713135</v>
@@ -5297,67 +5297,67 @@
         <v>21.64405457516934</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.213795763380972</v>
+        <v>4.213795763380984</v>
       </c>
       <c r="AU24" t="n">
         <v>0.3640105128288269</v>
       </c>
       <c r="AV24" t="n">
-        <v>72.70268874507903</v>
+        <v>0.1791649676383784</v>
       </c>
       <c r="AW24" t="n">
-        <v>84.12214573252854</v>
+        <v>-0.1126329949561544</v>
       </c>
       <c r="AX24" t="n">
-        <v>106.7102006984492</v>
+        <v>0.008755541862328187</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.1791649676383784</v>
+        <v>0.09086994414633764</v>
       </c>
       <c r="AZ24" t="n">
-        <v>-0.1126329949561544</v>
+        <v>0.3563373646837604</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.008755541862328187</v>
+        <v>0.1058477036496406</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.09086994414633764</v>
+        <v>0.7624139177038316</v>
       </c>
       <c r="BC24" t="n">
-        <v>0.3563373646837604</v>
+        <v>0.1932134019567577</v>
       </c>
       <c r="BD24" t="n">
-        <v>0.1058477036496406</v>
+        <v>0.7884979248046875</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.7624139177038316</v>
+        <v>0.09495552549970654</v>
       </c>
       <c r="BF24" t="n">
-        <v>0.1932134019567577</v>
+        <v>72.70268874507912</v>
       </c>
       <c r="BG24" t="n">
-        <v>0.7884979248046875</v>
+        <v>84.12214573252855</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.09495552549970654</v>
+        <v>106.7102006984491</v>
       </c>
       <c r="BI24" t="n">
         <v>-1.364635899951743</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.1470869587981625</v>
+        <v>0.1470869587981305</v>
       </c>
       <c r="BK24" t="n">
-        <v>-1.255597045288972</v>
+        <v>-1.255597045289001</v>
       </c>
       <c r="BL24" t="n">
-        <v>-0.3753748214716452</v>
+        <v>-0.3753748214716701</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.2020139804532874</v>
+        <v>0.202013980453259</v>
       </c>
       <c r="BN24" t="n">
-        <v>0.823352245824406</v>
+        <v>0.8233522458244273</v>
       </c>
     </row>
     <row r="25">
@@ -5371,7 +5371,7 @@
         <v>147.7156781135722</v>
       </c>
       <c r="D25" t="n">
-        <v>6.180929630360708</v>
+        <v>6.180929630360705</v>
       </c>
       <c r="E25" t="n">
         <v>0.9995930790901184</v>
@@ -5389,7 +5389,7 @@
         <v>135.3021012975815</v>
       </c>
       <c r="J25" t="n">
-        <v>2.180870543134972</v>
+        <v>2.180870543134974</v>
       </c>
       <c r="K25" t="n">
         <v>0.9977676868438721</v>
@@ -5398,7 +5398,7 @@
         <v>130.0330872231341</v>
       </c>
       <c r="M25" t="n">
-        <v>3.355586275141292</v>
+        <v>3.35558627514129</v>
       </c>
       <c r="N25" t="n">
         <v>0.9924861192703247</v>
@@ -5407,7 +5407,7 @@
         <v>115.932042547997</v>
       </c>
       <c r="P25" t="n">
-        <v>8.518624812998667</v>
+        <v>8.51862481299867</v>
       </c>
       <c r="Q25" t="n">
         <v>0.9781308770179749</v>
@@ -5416,7 +5416,7 @@
         <v>122.3022623265043</v>
       </c>
       <c r="S25" t="n">
-        <v>14.51631911257482</v>
+        <v>14.5163191125748</v>
       </c>
       <c r="T25" t="n">
         <v>0.9932678937911987</v>
@@ -5425,7 +5425,7 @@
         <v>119.0502653730677</v>
       </c>
       <c r="V25" t="n">
-        <v>22.82206758539729</v>
+        <v>22.82206758539727</v>
       </c>
       <c r="W25" t="n">
         <v>0.9869035482406616</v>
@@ -5434,7 +5434,7 @@
         <v>72.73493827657497</v>
       </c>
       <c r="Y25" t="n">
-        <v>27.34619302952544</v>
+        <v>27.34619302952543</v>
       </c>
       <c r="Z25" t="n">
         <v>0.9905477166175842</v>
@@ -5443,7 +5443,7 @@
         <v>69.26956176757812</v>
       </c>
       <c r="AB25" t="n">
-        <v>18.94047513921211</v>
+        <v>18.9404751392121</v>
       </c>
       <c r="AC25" t="n">
         <v>0.994828999042511</v>
@@ -5452,7 +5452,7 @@
         <v>76.41392971606965</v>
       </c>
       <c r="AE25" t="n">
-        <v>13.0970894022191</v>
+        <v>13.09708940221908</v>
       </c>
       <c r="AF25" t="n">
         <v>0.9893146753311157</v>
@@ -5461,7 +5461,7 @@
         <v>67.68316309502785</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.871611899517944</v>
+        <v>4.871611899517952</v>
       </c>
       <c r="AI25" t="n">
         <v>0.9957537651062012</v>
@@ -5470,7 +5470,7 @@
         <v>75.9483093911029</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.4319535925033335</v>
+        <v>0.4319535925033245</v>
       </c>
       <c r="AL25" t="n">
         <v>0.9975041747093201</v>
@@ -5497,67 +5497,67 @@
         <v>24.16431345838182</v>
       </c>
       <c r="AT25" t="n">
-        <v>12.98967726687167</v>
+        <v>12.98967726687168</v>
       </c>
       <c r="AU25" t="n">
         <v>0.04723560065031052</v>
       </c>
       <c r="AV25" t="n">
+        <v>-0.01757195655335408</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>-0.1160702806838003</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.3080834733678941</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.08893317364631415</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.7360539537795034</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0.08422567489299482</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.026064284304354</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>-0.112222103362388</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.029412289883226</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0.0634294875124688</v>
+      </c>
+      <c r="BF25" t="n">
         <v>71.53577134821245</v>
       </c>
-      <c r="AW25" t="n">
-        <v>82.57288228121499</v>
-      </c>
-      <c r="AX25" t="n">
+      <c r="BG25" t="n">
+        <v>82.57288228121494</v>
+      </c>
+      <c r="BH25" t="n">
         <v>106.8751674242842</v>
       </c>
-      <c r="AY25" t="n">
-        <v>-0.01757195655335408</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>-0.1160702806838003</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0.3080834733678941</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0.08893317364631415</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0.7360539537795034</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0.08422567489299482</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.026064284304354</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>-0.112222103362388</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.029412289883226</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>0.0634294875124688</v>
-      </c>
       <c r="BI25" t="n">
-        <v>-1.275138158142276</v>
+        <v>-1.275138158142319</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.1447919993631288</v>
+        <v>0.144791999363143</v>
       </c>
       <c r="BK25" t="n">
-        <v>-2.486833707524916</v>
+        <v>-2.486833707524944</v>
       </c>
       <c r="BL25" t="n">
-        <v>-0.2892323389508107</v>
+        <v>-0.2892323389507823</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.8573125270724944</v>
+        <v>0.8573125270725228</v>
       </c>
       <c r="BN25" t="n">
-        <v>-0.2113763902306722</v>
+        <v>-0.2113763902306687</v>
       </c>
     </row>
     <row r="26">
@@ -5571,7 +5571,7 @@
         <v>148.3880225648271</v>
       </c>
       <c r="D26" t="n">
-        <v>6.604117535530264</v>
+        <v>6.604117535530253</v>
       </c>
       <c r="E26" t="n">
         <v>0.999508261680603</v>
@@ -5589,7 +5589,7 @@
         <v>135.5665653309924</v>
       </c>
       <c r="J26" t="n">
-        <v>1.799465747589778</v>
+        <v>1.799465747589761</v>
       </c>
       <c r="K26" t="n">
         <v>0.9973323345184326</v>
@@ -5598,7 +5598,7 @@
         <v>130.6320190429688</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3229097406915</v>
+        <v>3.32290974069149</v>
       </c>
       <c r="N26" t="n">
         <v>0.9974451065063477</v>
@@ -5607,7 +5607,7 @@
         <v>116.9592755906125</v>
       </c>
       <c r="P26" t="n">
-        <v>8.698305170586764</v>
+        <v>8.698305170586769</v>
       </c>
       <c r="Q26" t="n">
         <v>0.9832171201705933</v>
@@ -5625,7 +5625,7 @@
         <v>119.6190448517495</v>
       </c>
       <c r="V26" t="n">
-        <v>22.90383196891622</v>
+        <v>22.90383196891623</v>
       </c>
       <c r="W26" t="n">
         <v>0.9902080893516541</v>
@@ -5634,7 +5634,7 @@
         <v>73.93418170036153</v>
       </c>
       <c r="Y26" t="n">
-        <v>27.20840129446475</v>
+        <v>27.20840129446476</v>
       </c>
       <c r="Z26" t="n">
         <v>0.9880790114402771</v>
@@ -5643,7 +5643,7 @@
         <v>70.23511034377078</v>
       </c>
       <c r="AB26" t="n">
-        <v>18.72867016082114</v>
+        <v>18.72867016082115</v>
       </c>
       <c r="AC26" t="n">
         <v>0.9930351972579956</v>
@@ -5652,7 +5652,7 @@
         <v>77.27369754872424</v>
       </c>
       <c r="AE26" t="n">
-        <v>12.39268526117851</v>
+        <v>12.39268526117852</v>
       </c>
       <c r="AF26" t="n">
         <v>0.98696368932724</v>
@@ -5661,7 +5661,7 @@
         <v>67.88678676524061</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.279086498503972</v>
+        <v>5.27908649850399</v>
       </c>
       <c r="AI26" t="n">
         <v>0.9966609477996826</v>
@@ -5670,7 +5670,7 @@
         <v>75.77586884194233</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.1564837516622219</v>
+        <v>0.156483751662234</v>
       </c>
       <c r="AL26" t="n">
         <v>0.9976072311401367</v>
@@ -5688,7 +5688,7 @@
         <v>33.9147040184508</v>
       </c>
       <c r="AQ26" t="n">
-        <v>21.29047474962599</v>
+        <v>21.290474749626</v>
       </c>
       <c r="AR26" t="n">
         <v>0.9021594524383545</v>
@@ -5697,67 +5697,67 @@
         <v>22.94810477723467</v>
       </c>
       <c r="AT26" t="n">
-        <v>12.90982834836268</v>
+        <v>12.9098283483627</v>
       </c>
       <c r="AU26" t="n">
         <v>0.4446131885051727</v>
       </c>
       <c r="AV26" t="n">
+        <v>-0.05297559372922223</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.01034838088014922</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.1866218891549565</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>-0.05327184149559727</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.5247887144697501</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>-0.1551303457706545</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0.5379697109790555</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>-0.1853902289207952</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0.9153568998296251</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>-0.1014100744369166</v>
+      </c>
+      <c r="BF26" t="n">
         <v>70.15241242879448</v>
       </c>
-      <c r="AW26" t="n">
-        <v>79.14847831747871</v>
-      </c>
-      <c r="AX26" t="n">
+      <c r="BG26" t="n">
+        <v>79.14847831747866</v>
+      </c>
+      <c r="BH26" t="n">
         <v>108.4248257525941</v>
       </c>
-      <c r="AY26" t="n">
-        <v>-0.05297559372922223</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0.01034838088014922</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0.1866218891549565</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>-0.05327184149559727</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0.5247887144697501</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>-0.1551303457706545</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0.5379697109790555</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>-0.1853902289207952</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>0.9153568998296251</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>-0.1014100744369166</v>
-      </c>
       <c r="BI26" t="n">
-        <v>-1.075051901225486</v>
+        <v>-1.075051901225457</v>
       </c>
       <c r="BJ26" t="n">
-        <v>-0.1234730012259959</v>
+        <v>-0.1234730012259604</v>
       </c>
       <c r="BK26" t="n">
-        <v>-1.834061723190594</v>
+        <v>-1.834061723190565</v>
       </c>
       <c r="BL26" t="n">
-        <v>1.153881039933339</v>
+        <v>1.15388103993336</v>
       </c>
       <c r="BM26" t="n">
-        <v>-0.220738800008057</v>
+        <v>-0.2207388000080783</v>
       </c>
       <c r="BN26" t="n">
-        <v>0.1708418749423615</v>
+        <v>0.1708418749423366</v>
       </c>
     </row>
     <row r="27">
@@ -5771,7 +5771,7 @@
         <v>149.3510144822141</v>
       </c>
       <c r="D27" t="n">
-        <v>6.691319891747014</v>
+        <v>6.691319891747009</v>
       </c>
       <c r="E27" t="n">
         <v>0.9998911619186401</v>
@@ -5780,7 +5780,7 @@
         <v>133.6842963036071</v>
       </c>
       <c r="G27" t="n">
-        <v>15.11353837682844</v>
+        <v>15.11353837682846</v>
       </c>
       <c r="H27" t="n">
         <v>0.9999364614486694</v>
@@ -5798,7 +5798,7 @@
         <v>130.6340237881275</v>
       </c>
       <c r="M27" t="n">
-        <v>3.514488707197472</v>
+        <v>3.514488707197474</v>
       </c>
       <c r="N27" t="n">
         <v>0.9981529116630554</v>
@@ -5807,7 +5807,7 @@
         <v>117.5304899824427</v>
       </c>
       <c r="P27" t="n">
-        <v>8.938192813954458</v>
+        <v>8.938192813954455</v>
       </c>
       <c r="Q27" t="n">
         <v>0.9817606806755066</v>
@@ -5816,7 +5816,7 @@
         <v>124.1011842768243</v>
       </c>
       <c r="S27" t="n">
-        <v>14.97049534574467</v>
+        <v>14.97049534574468</v>
       </c>
       <c r="T27" t="n">
         <v>0.9964591860771179</v>
@@ -5861,7 +5861,7 @@
         <v>68.05640687333776</v>
       </c>
       <c r="AH27" t="n">
-        <v>5.063596684881986</v>
+        <v>5.063596684881982</v>
       </c>
       <c r="AI27" t="n">
         <v>0.9958202838897705</v>
@@ -5870,7 +5870,7 @@
         <v>75.84235820364445</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.1184991065491943</v>
+        <v>-0.1184991065492021</v>
       </c>
       <c r="AL27" t="n">
         <v>0.9979414343833923</v>
@@ -5879,7 +5879,7 @@
         <v>57.22861594342172</v>
       </c>
       <c r="AN27" t="n">
-        <v>21.40428259017619</v>
+        <v>21.4042825901762</v>
       </c>
       <c r="AO27" t="n">
         <v>0.9983164072036743</v>
@@ -5888,7 +5888,7 @@
         <v>32.46960538498899</v>
       </c>
       <c r="AQ27" t="n">
-        <v>21.3162198979804</v>
+        <v>21.31621989798039</v>
       </c>
       <c r="AR27" t="n">
         <v>0.9012982249259949</v>
@@ -5897,67 +5897,67 @@
         <v>20.08478692237367</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.606947229263625</v>
+        <v>8.60694722926363</v>
       </c>
       <c r="AU27" t="n">
         <v>0.4266870617866516</v>
       </c>
       <c r="AV27" t="n">
-        <v>69.38566754576148</v>
+        <v>0.003124805206944359</v>
       </c>
       <c r="AW27" t="n">
-        <v>78.9047588348338</v>
+        <v>-0.1085585736213837</v>
       </c>
       <c r="AX27" t="n">
+        <v>0.2015397903766996</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>-0.1310581856585529</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0.4257932622381944</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0.04356465441115276</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0.6552838264627638</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0.2606391906738281</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0.8265921410093924</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0.0142036600315798</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>69.38566754576154</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>78.90475883483381</v>
+      </c>
+      <c r="BH27" t="n">
         <v>106.433689824268</v>
       </c>
-      <c r="AY27" t="n">
-        <v>0.003124805206944359</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>-0.1085585736213837</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0.2015397903766996</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>-0.1310581856585529</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0.4257932622381944</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0.04356465441115276</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0.6552838264627638</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0.2606391906738281</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0.8265921410093924</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>0.0142036600315798</v>
-      </c>
       <c r="BI27" t="n">
-        <v>-1.522084160594268</v>
+        <v>-1.52208416059424</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-1.018491914274435</v>
+        <v>-1.018491914274467</v>
       </c>
       <c r="BK27" t="n">
-        <v>-0.1790716276582387</v>
+        <v>-0.1790716276582245</v>
       </c>
       <c r="BL27" t="n">
-        <v>0.6313007658683318</v>
+        <v>0.6313007658683176</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.198996276957217</v>
+        <v>1.198996276957196</v>
       </c>
       <c r="BN27" t="n">
-        <v>1.834546494135711</v>
+        <v>1.834546494135729</v>
       </c>
     </row>
     <row r="28">
@@ -5971,7 +5971,7 @@
         <v>150.0898482951712</v>
       </c>
       <c r="D28" t="n">
-        <v>6.783310910488723</v>
+        <v>6.783310910488697</v>
       </c>
       <c r="E28" t="n">
         <v>0.9999438524246216</v>
@@ -5980,7 +5980,7 @@
         <v>134.2329390505527</v>
       </c>
       <c r="G28" t="n">
-        <v>15.2150093240941</v>
+        <v>15.21500932409408</v>
       </c>
       <c r="H28" t="n">
         <v>0.9999159574508667</v>
@@ -5989,7 +5989,7 @@
         <v>135.7737033925158</v>
       </c>
       <c r="J28" t="n">
-        <v>1.735427531790236</v>
+        <v>1.735427531790226</v>
       </c>
       <c r="K28" t="n">
         <v>0.9980829954147339</v>
@@ -5998,7 +5998,7 @@
         <v>130.7973009474734</v>
       </c>
       <c r="M28" t="n">
-        <v>3.562683754778931</v>
+        <v>3.562683754778923</v>
       </c>
       <c r="N28" t="n">
         <v>0.998455286026001</v>
@@ -6007,7 +6007,7 @@
         <v>118.6751264206907</v>
       </c>
       <c r="P28" t="n">
-        <v>9.160289358585459</v>
+        <v>9.160289358585439</v>
       </c>
       <c r="Q28" t="n">
         <v>0.982352077960968</v>
@@ -6025,7 +6025,7 @@
         <v>121.2601357317985</v>
       </c>
       <c r="V28" t="n">
-        <v>23.21475414519617</v>
+        <v>23.21475414519615</v>
       </c>
       <c r="W28" t="n">
         <v>0.9871582388877869</v>
@@ -6034,7 +6034,7 @@
         <v>75.58736598238032</v>
       </c>
       <c r="Y28" t="n">
-        <v>26.51979973975651</v>
+        <v>26.51979973975648</v>
       </c>
       <c r="Z28" t="n">
         <v>0.9948260188102722</v>
@@ -6052,7 +6052,7 @@
         <v>78.12528407320063</v>
       </c>
       <c r="AE28" t="n">
-        <v>11.12589734665892</v>
+        <v>11.12589734665891</v>
       </c>
       <c r="AF28" t="n">
         <v>0.987898051738739</v>
@@ -6061,7 +6061,7 @@
         <v>68.28986634599401</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.817946413730056</v>
+        <v>4.817946413730054</v>
       </c>
       <c r="AI28" t="n">
         <v>0.9966981410980225</v>
@@ -6070,7 +6070,7 @@
         <v>75.78211845235622</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.3186652000914023</v>
+        <v>-0.3186652000914229</v>
       </c>
       <c r="AL28" t="n">
         <v>0.9974205493927002</v>
@@ -6079,7 +6079,7 @@
         <v>58.66967465015168</v>
       </c>
       <c r="AN28" t="n">
-        <v>20.18181009495513</v>
+        <v>20.18181009495512</v>
       </c>
       <c r="AO28" t="n">
         <v>0.9990237951278687</v>
@@ -6088,7 +6088,7 @@
         <v>30.38607252405045</v>
       </c>
       <c r="AQ28" t="n">
-        <v>21.17127763464097</v>
+        <v>21.17127763464096</v>
       </c>
       <c r="AR28" t="n">
         <v>0.8989769816398621</v>
@@ -6097,67 +6097,67 @@
         <v>18.08034004049098</v>
       </c>
       <c r="AT28" t="n">
-        <v>10.12173916431186</v>
+        <v>10.12173916431184</v>
       </c>
       <c r="AU28" t="n">
         <v>0.1662403345108032</v>
       </c>
       <c r="AV28" t="n">
-        <v>67.10824410760594</v>
+        <v>-0.2700927409719895</v>
       </c>
       <c r="AW28" t="n">
-        <v>78.79033506216223</v>
+        <v>-0.1520156860351527</v>
       </c>
       <c r="AX28" t="n">
-        <v>110.8228183065086</v>
+        <v>-0.07549448216214927</v>
       </c>
       <c r="AY28" t="n">
-        <v>-0.2700927409719895</v>
+        <v>-0.1987964548963141</v>
       </c>
       <c r="AZ28" t="n">
-        <v>-0.1520156860351527</v>
+        <v>0.6119180232920556</v>
       </c>
       <c r="BA28" t="n">
-        <v>-0.07549448216214927</v>
+        <v>-0.04502154411153469</v>
       </c>
       <c r="BB28" t="n">
-        <v>-0.1987964548963141</v>
+        <v>1.059248092326712</v>
       </c>
       <c r="BC28" t="n">
-        <v>0.6119180232920556</v>
+        <v>0.04679903070977431</v>
       </c>
       <c r="BD28" t="n">
-        <v>-0.04502154411153469</v>
+        <v>0.9437642198927847</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.059248092326712</v>
+        <v>-0.1421624041618195</v>
       </c>
       <c r="BF28" t="n">
-        <v>0.04679903070977431</v>
+        <v>67.108244107606</v>
       </c>
       <c r="BG28" t="n">
-        <v>0.9437642198927847</v>
+        <v>78.79033506216221</v>
       </c>
       <c r="BH28" t="n">
-        <v>-0.1421624041618195</v>
+        <v>110.8228183065085</v>
       </c>
       <c r="BI28" t="n">
-        <v>-3.112035729774355</v>
+        <v>-3.112035729774391</v>
       </c>
       <c r="BJ28" t="n">
-        <v>-0.08158966341411933</v>
+        <v>-0.08158966341414775</v>
       </c>
       <c r="BK28" t="n">
         <v>-0.5714601914539301</v>
       </c>
       <c r="BL28" t="n">
-        <v>-0.7796432546618277</v>
+        <v>-0.7796432546618348</v>
       </c>
       <c r="BM28" t="n">
-        <v>3.448354188263366</v>
+        <v>3.44835418826338</v>
       </c>
       <c r="BN28" t="n">
-        <v>0.7600370311918638</v>
+        <v>0.7600370311919029</v>
       </c>
     </row>
     <row r="29">
@@ -6171,7 +6171,7 @@
         <v>150.7424212516623</v>
       </c>
       <c r="D29" t="n">
-        <v>6.769789026138653</v>
+        <v>6.769789026138631</v>
       </c>
       <c r="E29" t="n">
         <v>0.9999443292617798</v>
@@ -6189,7 +6189,7 @@
         <v>135.8045293929729</v>
       </c>
       <c r="J29" t="n">
-        <v>1.852335828415903</v>
+        <v>1.852335828415891</v>
       </c>
       <c r="K29" t="n">
         <v>0.9984903335571289</v>
@@ -6198,7 +6198,7 @@
         <v>130.851859234749</v>
       </c>
       <c r="M29" t="n">
-        <v>3.528383944896945</v>
+        <v>3.528383944896942</v>
       </c>
       <c r="N29" t="n">
         <v>0.9986429810523987</v>
@@ -6207,7 +6207,7 @@
         <v>118.6966672856757</v>
       </c>
       <c r="P29" t="n">
-        <v>9.343021473986056</v>
+        <v>9.343021473986038</v>
       </c>
       <c r="Q29" t="n">
         <v>0.9839648008346558</v>
@@ -6216,7 +6216,7 @@
         <v>125.6732129036112</v>
       </c>
       <c r="S29" t="n">
-        <v>15.40382872236538</v>
+        <v>15.40382872236536</v>
       </c>
       <c r="T29" t="n">
         <v>0.9970954656600952</v>
@@ -6225,7 +6225,7 @@
         <v>121.9045354964885</v>
       </c>
       <c r="V29" t="n">
-        <v>23.47020899995846</v>
+        <v>23.47020899995844</v>
       </c>
       <c r="W29" t="n">
         <v>0.992119312286377</v>
@@ -6243,7 +6243,7 @@
         <v>72.46399737418966</v>
       </c>
       <c r="AB29" t="n">
-        <v>18.11935749459775</v>
+        <v>18.11935749459774</v>
       </c>
       <c r="AC29" t="n">
         <v>0.9940286874771118</v>
@@ -6261,7 +6261,7 @@
         <v>67.90541790901347</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.03473484769782</v>
+        <v>5.034734847697806</v>
       </c>
       <c r="AI29" t="n">
         <v>0.9970257878303528</v>
@@ -6270,7 +6270,7 @@
         <v>75.30217272170047</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.1472797799617638</v>
+        <v>-0.1472797799617686</v>
       </c>
       <c r="AL29" t="n">
         <v>0.9976770281791687</v>
@@ -6279,7 +6279,7 @@
         <v>59.94675007272274</v>
       </c>
       <c r="AN29" t="n">
-        <v>19.91810900099733</v>
+        <v>19.91810900099734</v>
       </c>
       <c r="AO29" t="n">
         <v>0.9998419284820557</v>
@@ -6288,7 +6288,7 @@
         <v>30.69491082049431</v>
       </c>
       <c r="AQ29" t="n">
-        <v>21.37149242644614</v>
+        <v>21.37149242644615</v>
       </c>
       <c r="AR29" t="n">
         <v>0.9370473623275757</v>
@@ -6297,67 +6297,67 @@
         <v>13.08892534134236</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.941350409325139</v>
+        <v>5.941350409325134</v>
       </c>
       <c r="AU29" t="n">
         <v>0.7210322618484497</v>
       </c>
       <c r="AV29" t="n">
-        <v>63.16159608621277</v>
+        <v>-0.300906566863361</v>
       </c>
       <c r="AW29" t="n">
-        <v>77.76183845192594</v>
+        <v>0.1078727397512864</v>
       </c>
       <c r="AX29" t="n">
+        <v>-0.1960531194159287</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.1668544525795781</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.335750174015125</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>-0.03397515479554514</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0.7488818878823125</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>-0.09265250348030207</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0.5422673326857534</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>-0.2368886420067327</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>63.16159608621275</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>77.76183845192595</v>
+      </c>
+      <c r="BH29" t="n">
         <v>113.3303982007948</v>
       </c>
-      <c r="AY29" t="n">
-        <v>-0.300906566863361</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0.1078727397512864</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>-0.1960531194159287</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0.1668544525795781</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0.335750174015125</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>-0.03397515479554514</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0.7488818878823125</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>-0.09265250348030207</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0.5422673326857534</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>-0.2368886420067327</v>
-      </c>
       <c r="BI29" t="n">
-        <v>-1.685263487422507</v>
+        <v>-1.685263487422535</v>
       </c>
       <c r="BJ29" t="n">
-        <v>2.003340412722558</v>
+        <v>2.003340412722576</v>
       </c>
       <c r="BK29" t="n">
         <v>-1.738358136981894</v>
       </c>
       <c r="BL29" t="n">
-        <v>-0.3263818491687438</v>
+        <v>-0.3263818491687687</v>
       </c>
       <c r="BM29" t="n">
-        <v>2.719070339340945</v>
+        <v>2.719070339341002</v>
       </c>
       <c r="BN29" t="n">
-        <v>-0.004487906315063128</v>
+        <v>-0.004487906315073786</v>
       </c>
     </row>
     <row r="30">
@@ -6371,7 +6371,7 @@
         <v>151.6472025120512</v>
       </c>
       <c r="D30" t="n">
-        <v>7.073520092254</v>
+        <v>7.07352009225399</v>
       </c>
       <c r="E30" t="n">
         <v>0.9997450709342957</v>
@@ -6389,7 +6389,7 @@
         <v>135.8232944569689</v>
       </c>
       <c r="J30" t="n">
-        <v>1.893307300324125</v>
+        <v>1.893307300324136</v>
       </c>
       <c r="K30" t="n">
         <v>0.9986369013786316</v>
@@ -6398,7 +6398,7 @@
         <v>130.9292813564869</v>
       </c>
       <c r="M30" t="n">
-        <v>3.70592157891457</v>
+        <v>3.705921578914561</v>
       </c>
       <c r="N30" t="n">
         <v>0.9989929795265198</v>
@@ -6407,7 +6407,7 @@
         <v>119.1162839848945</v>
       </c>
       <c r="P30" t="n">
-        <v>9.42514297810007</v>
+        <v>9.425142978100068</v>
       </c>
       <c r="Q30" t="n">
         <v>0.9808506965637207</v>
@@ -6416,7 +6416,7 @@
         <v>125.9468484432139</v>
       </c>
       <c r="S30" t="n">
-        <v>15.40230284345913</v>
+        <v>15.40230284345911</v>
       </c>
       <c r="T30" t="n">
         <v>0.9956576824188232</v>
@@ -6425,7 +6425,7 @@
         <v>122.6035178975856</v>
       </c>
       <c r="V30" t="n">
-        <v>23.62218004591921</v>
+        <v>23.62218004591922</v>
       </c>
       <c r="W30" t="n">
         <v>0.9926285743713379</v>
@@ -6434,7 +6434,7 @@
         <v>76.67190064775183</v>
       </c>
       <c r="Y30" t="n">
-        <v>25.84565345277176</v>
+        <v>25.84565345277178</v>
       </c>
       <c r="Z30" t="n">
         <v>0.989920973777771</v>
@@ -6443,7 +6443,7 @@
         <v>73.04344177246094</v>
       </c>
       <c r="AB30" t="n">
-        <v>17.28164997506647</v>
+        <v>17.28164997506649</v>
       </c>
       <c r="AC30" t="n">
         <v>0.9950897097587585</v>
@@ -6461,7 +6461,7 @@
         <v>67.89776010716216</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.273762155086416</v>
+        <v>5.273762155086437</v>
       </c>
       <c r="AI30" t="n">
         <v>0.9988054037094116</v>
@@ -6470,7 +6470,7 @@
         <v>75.18030531862949</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.3440369950964168</v>
+        <v>-0.3440369950964096</v>
       </c>
       <c r="AL30" t="n">
         <v>0.9976281523704529</v>
@@ -6488,7 +6488,7 @@
         <v>34.40646719425283</v>
       </c>
       <c r="AQ30" t="n">
-        <v>20.44291394822142</v>
+        <v>20.44291394822141</v>
       </c>
       <c r="AR30" t="n">
         <v>0.9570081233978271</v>
@@ -6497,67 +6497,67 @@
         <v>9.867574813518118</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.535355588223069</v>
+        <v>6.535355588223072</v>
       </c>
       <c r="AU30" t="n">
         <v>0.9884782433509827</v>
       </c>
       <c r="AV30" t="n">
+        <v>-0.05434726146941671</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.1624553761583662</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.2582144229970069</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.218878401086684</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.5439677137009653</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0.2213498379321841</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0.8739430853661077</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0.0699022982982882</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.4699869358793194</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0.04994615595391849</v>
+      </c>
+      <c r="BF30" t="n">
         <v>63.73771713276093</v>
       </c>
-      <c r="AW30" t="n">
-        <v>75.31361878819844</v>
-      </c>
-      <c r="AX30" t="n">
+      <c r="BG30" t="n">
+        <v>75.31361878819843</v>
+      </c>
+      <c r="BH30" t="n">
         <v>116.2609589851905</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>-0.05434726146941671</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0.1624553761583662</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0.2582144229970069</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0.218878401086684</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0.5439677137009653</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0.2213498379321841</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0.8739430853661077</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0.0699022982982882</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0.4699869358793194</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>0.04994615595391849</v>
       </c>
       <c r="BI30" t="n">
         <v>0.8946450956707608</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.6304932329436852</v>
+        <v>0.6304932329437118</v>
       </c>
       <c r="BK30" t="n">
-        <v>-1.224223889791418</v>
+        <v>-1.224223889791467</v>
       </c>
       <c r="BL30" t="n">
-        <v>-0.3117752858632947</v>
+        <v>-0.3117752858632841</v>
       </c>
       <c r="BM30" t="n">
-        <v>3.43937837563324</v>
+        <v>3.439378375633233</v>
       </c>
       <c r="BN30" t="n">
-        <v>-0.1779420390105528</v>
+        <v>-0.1779420390106061</v>
       </c>
     </row>
     <row r="31">
@@ -6571,7 +6571,7 @@
         <v>152.3459251890791</v>
       </c>
       <c r="D31" t="n">
-        <v>7.154067019198806</v>
+        <v>7.154067019198804</v>
       </c>
       <c r="E31" t="n">
         <v>0.9995471835136414</v>
@@ -6580,7 +6580,7 @@
         <v>135.9196358538689</v>
       </c>
       <c r="G31" t="n">
-        <v>15.64373259848739</v>
+        <v>15.64373259848737</v>
       </c>
       <c r="H31" t="n">
         <v>0.9999573230743408</v>
@@ -6589,7 +6589,7 @@
         <v>136.0207496805394</v>
       </c>
       <c r="J31" t="n">
-        <v>1.650611390458778</v>
+        <v>1.650611390458777</v>
       </c>
       <c r="K31" t="n">
         <v>0.9988835453987122</v>
@@ -6598,7 +6598,7 @@
         <v>131.2204645035115</v>
       </c>
       <c r="M31" t="n">
-        <v>3.750577886053861</v>
+        <v>3.750577886053857</v>
       </c>
       <c r="N31" t="n">
         <v>0.9993208646774292</v>
@@ -6607,7 +6607,7 @@
         <v>119.3738653304729</v>
       </c>
       <c r="P31" t="n">
-        <v>9.565880958070153</v>
+        <v>9.565880958070148</v>
       </c>
       <c r="Q31" t="n">
         <v>0.9826788902282715</v>
@@ -6634,7 +6634,7 @@
         <v>77.39315438777842</v>
       </c>
       <c r="Y31" t="n">
-        <v>25.90625844103224</v>
+        <v>25.90625844103225</v>
       </c>
       <c r="Z31" t="n">
         <v>0.9926550388336182</v>
@@ -6652,7 +6652,7 @@
         <v>79.77527861899519</v>
       </c>
       <c r="AE31" t="n">
-        <v>10.69129781520112</v>
+        <v>10.69129781520113</v>
       </c>
       <c r="AF31" t="n">
         <v>0.9628118276596069</v>
@@ -6661,7 +6661,7 @@
         <v>68.42184675500748</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.604309731341402</v>
+        <v>5.604309731341424</v>
       </c>
       <c r="AI31" t="n">
         <v>0.9989421963691711</v>
@@ -6670,7 +6670,7 @@
         <v>75.19347819876164</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.2440594612284031</v>
+        <v>-0.244059461228391</v>
       </c>
       <c r="AL31" t="n">
         <v>0.9973064661026001</v>
@@ -6679,7 +6679,7 @@
         <v>62.3915286774331</v>
       </c>
       <c r="AN31" t="n">
-        <v>18.60921332176696</v>
+        <v>18.60921332176695</v>
       </c>
       <c r="AO31" t="n">
         <v>0.999669075012207</v>
@@ -6688,7 +6688,7 @@
         <v>35.28433860616481</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19.79986961851728</v>
+        <v>19.79986961851729</v>
       </c>
       <c r="AR31" t="n">
         <v>0.9773507118225098</v>
@@ -6697,67 +6697,67 @@
         <v>8.145281101794954</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.967798760596736</v>
+        <v>7.967798760596742</v>
       </c>
       <c r="AU31" t="n">
         <v>0.9828101396560669</v>
       </c>
       <c r="AV31" t="n">
-        <v>64.95088627755429</v>
+        <v>0.02400418545337146</v>
       </c>
       <c r="AW31" t="n">
-        <v>75.3133906723431</v>
+        <v>0.009723419838763903</v>
       </c>
       <c r="AX31" t="n">
+        <v>0.2417036827574393</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>-0.1302414752067378</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.7784498498794932</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>-0.03381079815804</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0.8886864844788889</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>-0.008122464443772515</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.6421596445935904</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0.1376923094404532</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>64.95088627755428</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>75.31339067234302</v>
+      </c>
+      <c r="BH31" t="n">
         <v>120.2091549520613</v>
       </c>
-      <c r="AY31" t="n">
-        <v>0.02400418545337146</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0.009723419838763903</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0.2417036827574393</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>-0.1302414752067378</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0.7784498498794932</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>-0.03381079815804</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0.8886864844788889</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>-0.008122464443772515</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0.6421596445935904</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>0.1376923094404532</v>
-      </c>
       <c r="BI31" t="n">
-        <v>-0.4242770215351364</v>
+        <v>-0.4242770215351115</v>
       </c>
       <c r="BJ31" t="n">
-        <v>-1.676897348299317</v>
+        <v>-1.676897348299288</v>
       </c>
       <c r="BK31" t="n">
-        <v>-2.361908708708484</v>
+        <v>-2.361908708708462</v>
       </c>
       <c r="BL31" t="n">
-        <v>-0.6041584531521913</v>
+        <v>-0.6041584531521309</v>
       </c>
       <c r="BM31" t="n">
-        <v>2.363186261319839</v>
+        <v>2.36318626131979</v>
       </c>
       <c r="BN31" t="n">
-        <v>0.06117889500381679</v>
+        <v>0.06117889500379903</v>
       </c>
     </row>
     <row r="32">
@@ -6771,7 +6771,7 @@
         <v>153.1336682908079</v>
       </c>
       <c r="D32" t="n">
-        <v>6.849069798246347</v>
+        <v>6.849069798246344</v>
       </c>
       <c r="E32" t="n">
         <v>0.9997374415397644</v>
@@ -6780,7 +6780,7 @@
         <v>136.8855740161652</v>
       </c>
       <c r="G32" t="n">
-        <v>15.79659644593585</v>
+        <v>15.79659644593584</v>
       </c>
       <c r="H32" t="n">
         <v>0.9999669790267944</v>
@@ -6789,7 +6789,7 @@
         <v>136.0919465409949</v>
       </c>
       <c r="J32" t="n">
-        <v>1.641456117021278</v>
+        <v>1.641456117021277</v>
       </c>
       <c r="K32" t="n">
         <v>0.9989355206489563</v>
@@ -6798,7 +6798,7 @@
         <v>131.4773640734084</v>
       </c>
       <c r="M32" t="n">
-        <v>3.648441395861056</v>
+        <v>3.648441395861037</v>
       </c>
       <c r="N32" t="n">
         <v>0.9992316961288452</v>
@@ -6807,7 +6807,7 @@
         <v>120.3583737637134</v>
       </c>
       <c r="P32" t="n">
-        <v>9.712056910738056</v>
+        <v>9.712056910738033</v>
       </c>
       <c r="Q32" t="n">
         <v>0.9896017909049988</v>
@@ -6816,7 +6816,7 @@
         <v>127.1729895409117</v>
       </c>
       <c r="S32" t="n">
-        <v>15.7218283795296</v>
+        <v>15.72182837952959</v>
       </c>
       <c r="T32" t="n">
         <v>0.9954753518104553</v>
@@ -6825,7 +6825,7 @@
         <v>123.5367145944149</v>
       </c>
       <c r="V32" t="n">
-        <v>24.0276580161237</v>
+        <v>24.02765801612367</v>
       </c>
       <c r="W32" t="n">
         <v>0.9888852834701538</v>
@@ -6861,7 +6861,7 @@
         <v>68.38116747267703</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.258928014877</v>
+        <v>6.258928014876995</v>
       </c>
       <c r="AI32" t="n">
         <v>0.9993318915367126</v>
@@ -6870,7 +6870,7 @@
         <v>75.22831368953624</v>
       </c>
       <c r="AK32" t="n">
-        <v>-0.3303852487117638</v>
+        <v>-0.3303852487117686</v>
       </c>
       <c r="AL32" t="n">
         <v>0.9964038133621216</v>
@@ -6879,7 +6879,7 @@
         <v>63.48676072790268</v>
       </c>
       <c r="AN32" t="n">
-        <v>18.26110190533578</v>
+        <v>18.26110190533577</v>
       </c>
       <c r="AO32" t="n">
         <v>0.9997571110725403</v>
@@ -6897,67 +6897,67 @@
         <v>7.88023776196419</v>
       </c>
       <c r="AT32" t="n">
-        <v>7.81639586103725</v>
+        <v>7.816395861037234</v>
       </c>
       <c r="AU32" t="n">
         <v>0.984545111656189</v>
       </c>
       <c r="AV32" t="n">
-        <v>62.88916308969065</v>
+        <v>-0.0349004217918889</v>
       </c>
       <c r="AW32" t="n">
-        <v>70.58980137078147</v>
+        <v>-0.08976510230530721</v>
       </c>
       <c r="AX32" t="n">
+        <v>-0.002268527416468658</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>-0.139704156429211</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0.4763461173848853</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>-0.1863357868600417</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0.8576981564785626</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>-0.03332787371696</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0.7453715547602258</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0.1037658529078662</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>62.8891630896907</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>70.5898013707815</v>
+      </c>
+      <c r="BH32" t="n">
         <v>120.9873315078301</v>
       </c>
-      <c r="AY32" t="n">
-        <v>-0.0349004217918889</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>-0.08976510230530721</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>-0.002268527416468658</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>-0.139704156429211</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0.4763461173848853</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>-0.1863357868600417</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0.8576981564785626</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>-0.03332787371696</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0.7453715547602258</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>0.1037658529078662</v>
-      </c>
       <c r="BI32" t="n">
-        <v>-2.459149600927873</v>
+        <v>-2.459149600927816</v>
       </c>
       <c r="BJ32" t="n">
-        <v>-1.306221609503154</v>
+        <v>-1.306221609503169</v>
       </c>
       <c r="BK32" t="n">
-        <v>-2.4325407960958</v>
+        <v>-2.432540796095729</v>
       </c>
       <c r="BL32" t="n">
-        <v>-0.1285256507989985</v>
+        <v>-0.1285256507990198</v>
       </c>
       <c r="BM32" t="n">
-        <v>3.561736165640873</v>
+        <v>3.561736165640831</v>
       </c>
       <c r="BN32" t="n">
-        <v>0.4089188649711417</v>
+        <v>0.4089188649711737</v>
       </c>
     </row>
     <row r="33">
@@ -6980,7 +6980,7 @@
         <v>137.7221614756483</v>
       </c>
       <c r="G33" t="n">
-        <v>15.89611946268286</v>
+        <v>15.89611946268285</v>
       </c>
       <c r="H33" t="n">
         <v>0.9999152421951294</v>
@@ -6989,7 +6989,7 @@
         <v>136.2441204963847</v>
       </c>
       <c r="J33" t="n">
-        <v>1.589381441156917</v>
+        <v>1.589381441156915</v>
       </c>
       <c r="K33" t="n">
         <v>0.9991065859794617</v>
@@ -7007,7 +7007,7 @@
         <v>120.8879511407081</v>
       </c>
       <c r="P33" t="n">
-        <v>9.917109063331139</v>
+        <v>9.917109063331118</v>
       </c>
       <c r="Q33" t="n">
         <v>0.9883447885513306</v>
@@ -7025,7 +7025,7 @@
         <v>124.1710987496883</v>
       </c>
       <c r="V33" t="n">
-        <v>24.17346061544217</v>
+        <v>24.17346061544216</v>
       </c>
       <c r="W33" t="n">
         <v>0.9904728531837463</v>
@@ -7034,7 +7034,7 @@
         <v>78.88389749729888</v>
       </c>
       <c r="Y33" t="n">
-        <v>25.42104518159908</v>
+        <v>25.42104518159907</v>
       </c>
       <c r="Z33" t="n">
         <v>0.9900087118148804</v>
@@ -7043,7 +7043,7 @@
         <v>75.927279857879</v>
       </c>
       <c r="AB33" t="n">
-        <v>17.0918403787816</v>
+        <v>17.09184037878158</v>
       </c>
       <c r="AC33" t="n">
         <v>0.989324152469635</v>
@@ -7061,7 +7061,7 @@
         <v>68.41730970017454</v>
       </c>
       <c r="AH33" t="n">
-        <v>6.762370657413584</v>
+        <v>6.762370657413564</v>
       </c>
       <c r="AI33" t="n">
         <v>0.9990819692611694</v>
@@ -7070,7 +7070,7 @@
         <v>75.12367735517786</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.294851749501305</v>
+        <v>-0.2948517495013298</v>
       </c>
       <c r="AL33" t="n">
         <v>0.9961444139480591</v>
@@ -7079,7 +7079,7 @@
         <v>64.09931994499044</v>
       </c>
       <c r="AN33" t="n">
-        <v>17.66897972593918</v>
+        <v>17.66897972593916</v>
       </c>
       <c r="AO33" t="n">
         <v>0.9998195767402649</v>
@@ -7088,7 +7088,7 @@
         <v>36.7787259690305</v>
       </c>
       <c r="AQ33" t="n">
-        <v>18.83626085646611</v>
+        <v>18.83626085646609</v>
       </c>
       <c r="AR33" t="n">
         <v>0.9397121071815491</v>
@@ -7097,67 +7097,67 @@
         <v>8.131216941995824</v>
       </c>
       <c r="AT33" t="n">
-        <v>6.352493610787917</v>
+        <v>6.352493610787899</v>
       </c>
       <c r="AU33" t="n">
         <v>0.9807446599006653</v>
       </c>
       <c r="AV33" t="n">
-        <v>60.03258707569854</v>
+        <v>-0.155526019157243</v>
       </c>
       <c r="AW33" t="n">
-        <v>70.4483090801515</v>
+        <v>-0.03145907787566316</v>
       </c>
       <c r="AX33" t="n">
-        <v>127.332627283343</v>
+        <v>-0.03770463010098268</v>
       </c>
       <c r="AY33" t="n">
-        <v>-0.155526019157243</v>
+        <v>0.08744178934299995</v>
       </c>
       <c r="AZ33" t="n">
-        <v>-0.03145907787566316</v>
+        <v>0.4057782761594098</v>
       </c>
       <c r="BA33" t="n">
-        <v>-0.03770463010098268</v>
+        <v>-0.2079091173537186</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.08744178934299995</v>
+        <v>0.8220307370449689</v>
       </c>
       <c r="BC33" t="n">
-        <v>0.4057782761594098</v>
+        <v>-0.2251178660291338</v>
       </c>
       <c r="BD33" t="n">
-        <v>-0.2079091173537186</v>
+        <v>0.8496913504093229</v>
       </c>
       <c r="BE33" t="n">
-        <v>0.8220307370449689</v>
+        <v>-0.06668618384828306</v>
       </c>
       <c r="BF33" t="n">
-        <v>-0.2251178660291338</v>
+        <v>60.03258707569864</v>
       </c>
       <c r="BG33" t="n">
-        <v>0.8496913504093229</v>
+        <v>70.44830908015156</v>
       </c>
       <c r="BH33" t="n">
-        <v>-0.06668618384828306</v>
+        <v>127.3326272833429</v>
       </c>
       <c r="BI33" t="n">
-        <v>-3.036720240541445</v>
+        <v>-3.036720240541449</v>
       </c>
       <c r="BJ33" t="n">
-        <v>1.262660958918849</v>
+        <v>1.262660958918795</v>
       </c>
       <c r="BK33" t="n">
-        <v>-2.618960010306481</v>
+        <v>-2.618960010306502</v>
       </c>
       <c r="BL33" t="n">
-        <v>1.446810692544425</v>
+        <v>1.446810692544378</v>
       </c>
       <c r="BM33" t="n">
-        <v>3.181023991262123</v>
+        <v>3.181023991262137</v>
       </c>
       <c r="BN33" t="n">
-        <v>-1.160589395010618</v>
+        <v>-1.160589395010589</v>
       </c>
     </row>
     <row r="34">
@@ -7171,7 +7171,7 @@
         <v>154.4189777780086</v>
       </c>
       <c r="D34" t="n">
-        <v>6.279056630236028</v>
+        <v>6.279056630236037</v>
       </c>
       <c r="E34" t="n">
         <v>0.9999440908432007</v>
@@ -7189,7 +7189,7 @@
         <v>136.3199112263132</v>
       </c>
       <c r="J34" t="n">
-        <v>1.62397344061668</v>
+        <v>1.623973440616689</v>
       </c>
       <c r="K34" t="n">
         <v>0.9990429282188416</v>
@@ -7198,7 +7198,7 @@
         <v>131.7371936554605</v>
       </c>
       <c r="M34" t="n">
-        <v>3.839208724650916</v>
+        <v>3.839208724650931</v>
       </c>
       <c r="N34" t="n">
         <v>0.9988478422164917</v>
@@ -7225,7 +7225,7 @@
         <v>124.7041742852394</v>
       </c>
       <c r="V34" t="n">
-        <v>24.32606473882146</v>
+        <v>24.32606473882148</v>
       </c>
       <c r="W34" t="n">
         <v>0.992497444152832</v>
@@ -7234,7 +7234,7 @@
         <v>79.65560263775765</v>
       </c>
       <c r="Y34" t="n">
-        <v>25.15977900078954</v>
+        <v>25.15977900078956</v>
       </c>
       <c r="Z34" t="n">
         <v>0.99299556016922</v>
@@ -7243,7 +7243,7 @@
         <v>76.46487621550865</v>
       </c>
       <c r="AB34" t="n">
-        <v>16.79885539602725</v>
+        <v>16.79885539602726</v>
       </c>
       <c r="AC34" t="n">
         <v>0.9926474094390869</v>
@@ -7252,7 +7252,7 @@
         <v>81.16524067330869</v>
       </c>
       <c r="AE34" t="n">
-        <v>9.206877363489014</v>
+        <v>9.20687736348903</v>
       </c>
       <c r="AF34" t="n">
         <v>0.952348530292511</v>
@@ -7261,7 +7261,7 @@
         <v>68.30575821247507</v>
       </c>
       <c r="AH34" t="n">
-        <v>7.601847547165875</v>
+        <v>7.601847547165892</v>
       </c>
       <c r="AI34" t="n">
         <v>0.9978728294372559</v>
@@ -7270,7 +7270,7 @@
         <v>74.91726165122175</v>
       </c>
       <c r="AK34" t="n">
-        <v>-0.1945170950382362</v>
+        <v>-0.1945170950382314</v>
       </c>
       <c r="AL34" t="n">
         <v>0.9950226545333862</v>
@@ -7297,64 +7297,64 @@
         <v>8.759197275689308</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.09206893596243</v>
+        <v>5.092068935962434</v>
       </c>
       <c r="AU34" t="n">
         <v>0.9457923769950867</v>
       </c>
       <c r="AV34" t="n">
-        <v>56.81572260860776</v>
+        <v>-0.09781857754321521</v>
       </c>
       <c r="AW34" t="n">
-        <v>65.35188135016851</v>
+        <v>-0.02561934450839587</v>
       </c>
       <c r="AX34" t="n">
+        <v>0.1726150512695312</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0.133301349396401</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0.06052788267744802</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>-0.1963554544651771</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0.4074624244202951</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>-0.1830364795441355</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0.6119991870636596</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>-0.1164436340332031</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>56.81572260860781</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>65.3518813501685</v>
+      </c>
+      <c r="BH34" t="n">
         <v>127.3493794903544</v>
       </c>
-      <c r="AY34" t="n">
-        <v>-0.09781857754321521</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>-0.02561934450839587</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0.1726150512695312</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0.133301349396401</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0.06052788267744802</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>-0.1963554544651771</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0.4074624244202951</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>-0.1830364795441355</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>0.6119991870636596</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>-0.1164436340332031</v>
-      </c>
       <c r="BI34" t="n">
-        <v>0.0661723169098245</v>
+        <v>0.06617231690977476</v>
       </c>
       <c r="BJ34" t="n">
-        <v>2.525719832521455</v>
+        <v>2.52571983252143</v>
       </c>
       <c r="BK34" t="n">
-        <v>0.4610805889930489</v>
+        <v>0.4610805889930276</v>
       </c>
       <c r="BL34" t="n">
-        <v>2.88827819262514</v>
+        <v>2.888278192625165</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.240557375619638</v>
+        <v>1.240557375619652</v>
       </c>
       <c r="BN34" t="n">
         <v>-0.7859839870275955</v>
@@ -7371,7 +7371,7 @@
         <v>154.9634730562251</v>
       </c>
       <c r="D35" t="n">
-        <v>6.228946117644625</v>
+        <v>6.228946117644615</v>
       </c>
       <c r="E35" t="n">
         <v>0.9999356269836426</v>
@@ -7380,7 +7380,7 @@
         <v>139.3608580244349</v>
       </c>
       <c r="G35" t="n">
-        <v>16.00830402780088</v>
+        <v>16.00830402780086</v>
       </c>
       <c r="H35" t="n">
         <v>0.9998958110809326</v>
@@ -7398,7 +7398,7 @@
         <v>131.8338921729555</v>
       </c>
       <c r="M35" t="n">
-        <v>3.703730157081111</v>
+        <v>3.703730157081117</v>
       </c>
       <c r="N35" t="n">
         <v>0.9992437362670898</v>
@@ -7425,7 +7425,7 @@
         <v>125.4747999475357</v>
       </c>
       <c r="V35" t="n">
-        <v>24.20487099505488</v>
+        <v>24.20487099505485</v>
       </c>
       <c r="W35" t="n">
         <v>0.9900258779525757</v>
@@ -7434,7 +7434,7 @@
         <v>80.10789587142619</v>
       </c>
       <c r="Y35" t="n">
-        <v>25.45229323366857</v>
+        <v>25.45229323366855</v>
       </c>
       <c r="Z35" t="n">
         <v>0.9939205646514893</v>
@@ -7443,7 +7443,7 @@
         <v>76.74220470671959</v>
       </c>
       <c r="AB35" t="n">
-        <v>17.37284558884642</v>
+        <v>17.37284558884641</v>
       </c>
       <c r="AC35" t="n">
         <v>0.99398273229599</v>
@@ -7452,7 +7452,7 @@
         <v>80.84902661911985</v>
       </c>
       <c r="AE35" t="n">
-        <v>9.507491740774611</v>
+        <v>9.507491740774602</v>
       </c>
       <c r="AF35" t="n">
         <v>0.9491029977798462</v>
@@ -7461,7 +7461,7 @@
         <v>68.7625398027136</v>
       </c>
       <c r="AH35" t="n">
-        <v>7.605857037483389</v>
+        <v>7.605857037483378</v>
       </c>
       <c r="AI35" t="n">
         <v>0.9976736903190613</v>
@@ -7470,7 +7470,7 @@
         <v>74.92804020009143</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.06894050760470805</v>
+        <v>-0.06894050760472074</v>
       </c>
       <c r="AL35" t="n">
         <v>0.9942591190338135</v>
@@ -7488,7 +7488,7 @@
         <v>35.52224585350524</v>
       </c>
       <c r="AQ35" t="n">
-        <v>16.28718274704954</v>
+        <v>16.28718274704953</v>
       </c>
       <c r="AR35" t="n">
         <v>0.9501581192016602</v>
@@ -7497,67 +7497,67 @@
         <v>10.66754929562832</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.408342726687181</v>
+        <v>3.408342726687168</v>
       </c>
       <c r="AU35" t="n">
         <v>0.7986185550689697</v>
       </c>
       <c r="AV35" t="n">
+        <v>-0.2067647081740347</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>-0.08900622104076916</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0.2288980686918194</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>-0.03789536496426393</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0.01306736722905555</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0.2166423391788541</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0.4559577779566979</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0.01977961114112148</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0.6168040823429166</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>-0.08678639188725512</v>
+      </c>
+      <c r="BF35" t="n">
         <v>60.16493170951819</v>
       </c>
-      <c r="AW35" t="n">
-        <v>71.3704702581376</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>129.8137420345823</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>-0.2067647081740347</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>-0.08900622104076916</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0.2288980686918194</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>-0.03789536496426393</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>0.01306736722905555</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0.2166423391788541</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>0.4559577779566979</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>0.01977961114112148</v>
-      </c>
       <c r="BG35" t="n">
-        <v>0.6168040823429166</v>
+        <v>71.37047025813762</v>
       </c>
       <c r="BH35" t="n">
-        <v>-0.08678639188725512</v>
+        <v>129.8137420345822</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.014719424501465</v>
+        <v>2.014719424501411</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0.430258073938564</v>
+        <v>0.4302580739385817</v>
       </c>
       <c r="BK35" t="n">
-        <v>3.1575963749438</v>
+        <v>3.157596374943829</v>
       </c>
       <c r="BL35" t="n">
         <v>-1.68411704058423</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.609056017206932</v>
+        <v>1.609056017206946</v>
       </c>
       <c r="BN35" t="n">
-        <v>-1.188715117058759</v>
+        <v>-1.188715117058745</v>
       </c>
     </row>
     <row r="36">
@@ -7571,7 +7571,7 @@
         <v>155.7732764710771</v>
       </c>
       <c r="D36" t="n">
-        <v>6.271962916597431</v>
+        <v>6.271962916597407</v>
       </c>
       <c r="E36" t="n">
         <v>0.9995213747024536</v>
@@ -7589,7 +7589,7 @@
         <v>136.2757419018035</v>
       </c>
       <c r="J36" t="n">
-        <v>1.478398099858708</v>
+        <v>1.47839809985871</v>
       </c>
       <c r="K36" t="n">
         <v>0.9991408586502075</v>
@@ -7598,7 +7598,7 @@
         <v>131.6559406037026</v>
       </c>
       <c r="M36" t="n">
-        <v>3.901623665018292</v>
+        <v>3.901623665018285</v>
       </c>
       <c r="N36" t="n">
         <v>0.9989416003227234</v>
@@ -7607,7 +7607,7 @@
         <v>121.6333024045254</v>
       </c>
       <c r="P36" t="n">
-        <v>10.63894718251331</v>
+        <v>10.6389471825133</v>
       </c>
       <c r="Q36" t="n">
         <v>0.9836435914039612</v>
@@ -7616,7 +7616,7 @@
         <v>129.4627088181516</v>
       </c>
       <c r="S36" t="n">
-        <v>16.29604583090926</v>
+        <v>16.29604583090924</v>
       </c>
       <c r="T36" t="n">
         <v>0.9952175617218018</v>
@@ -7634,7 +7634,7 @@
         <v>80.88921080244349</v>
       </c>
       <c r="Y36" t="n">
-        <v>25.63180314733629</v>
+        <v>25.63180314733627</v>
       </c>
       <c r="Z36" t="n">
         <v>0.9927655458450317</v>
@@ -7643,7 +7643,7 @@
         <v>77.37679177142205</v>
       </c>
       <c r="AB36" t="n">
-        <v>17.49804882293051</v>
+        <v>17.49804882293052</v>
       </c>
       <c r="AC36" t="n">
         <v>0.9931300282478333</v>
@@ -7652,7 +7652,7 @@
         <v>81.1913754077668</v>
       </c>
       <c r="AE36" t="n">
-        <v>9.703339921667236</v>
+        <v>9.70333992166722</v>
       </c>
       <c r="AF36" t="n">
         <v>0.9568681716918945</v>
@@ -7661,7 +7661,7 @@
         <v>68.76355434985871</v>
       </c>
       <c r="AH36" t="n">
-        <v>8.013461498504</v>
+        <v>8.01346149850399</v>
       </c>
       <c r="AI36" t="n">
         <v>0.9979698061943054</v>
@@ -7670,7 +7670,7 @@
         <v>74.50373223487368</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.3677530491605694</v>
+        <v>0.3677530491605718</v>
       </c>
       <c r="AL36" t="n">
         <v>0.9939133524894714</v>
@@ -7679,7 +7679,7 @@
         <v>66.16504750353225</v>
       </c>
       <c r="AN36" t="n">
-        <v>17.54341937125997</v>
+        <v>17.54341937125998</v>
       </c>
       <c r="AO36" t="n">
         <v>0.9993364214897156</v>
@@ -7697,67 +7697,67 @@
         <v>14.46707400869816</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.451359525639958</v>
+        <v>3.451359525639961</v>
       </c>
       <c r="AU36" t="n">
         <v>0.7720247507095337</v>
       </c>
       <c r="AV36" t="n">
-        <v>60.84516145761069</v>
+        <v>-0.2758310196247535</v>
       </c>
       <c r="AW36" t="n">
-        <v>71.66707410005611</v>
+        <v>0.01575185897502251</v>
       </c>
       <c r="AX36" t="n">
+        <v>0.09682432134100338</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>-0.01792298986556418</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0.4938125610351562</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0.1763364101978055</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0.4470216467025381</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0.0793883141050955</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0.4384264032891494</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>-0.08082085467399125</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>60.84516145761063</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>71.66707410005615</v>
+      </c>
+      <c r="BH36" t="n">
         <v>130.5674915247683</v>
       </c>
-      <c r="AY36" t="n">
-        <v>-0.2758310196247535</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0.01575185897502251</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0.09682432134100338</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>-0.01792298986556418</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>0.4938125610351562</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0.1763364101978055</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0.4470216467025381</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0.0793883141050955</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0.4384264032891494</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>-0.08082085467399125</v>
-      </c>
       <c r="BI36" t="n">
-        <v>0.9266884647869524</v>
+        <v>0.9266884647869382</v>
       </c>
       <c r="BJ36" t="n">
-        <v>-0.6971081924710987</v>
+        <v>-0.697108192471072</v>
       </c>
       <c r="BK36" t="n">
-        <v>-2.907153492175411</v>
+        <v>-2.907153492175432</v>
       </c>
       <c r="BL36" t="n">
-        <v>-1.967376248089209</v>
+        <v>-1.967376248089234</v>
       </c>
       <c r="BM36" t="n">
-        <v>-1.136872858497881</v>
+        <v>-1.136872858497838</v>
       </c>
       <c r="BN36" t="n">
-        <v>0.2486212330913382</v>
+        <v>0.248621233091324</v>
       </c>
     </row>
     <row r="37">
@@ -7771,7 +7771,7 @@
         <v>157.0841850118434</v>
       </c>
       <c r="D37" t="n">
-        <v>5.543469368143292</v>
+        <v>5.543469368143285</v>
       </c>
       <c r="E37" t="n">
         <v>0.9990569949150085</v>
@@ -7789,7 +7789,7 @@
         <v>136.2558243122507</v>
       </c>
       <c r="J37" t="n">
-        <v>1.265343199384972</v>
+        <v>1.265343199384974</v>
       </c>
       <c r="K37" t="n">
         <v>0.9993888139724731</v>
@@ -7798,7 +7798,7 @@
         <v>131.8131710620637</v>
       </c>
       <c r="M37" t="n">
-        <v>3.459654463098417</v>
+        <v>3.459654463098405</v>
       </c>
       <c r="N37" t="n">
         <v>0.9993249177932739</v>
@@ -7807,7 +7807,7 @@
         <v>122.7270735071061</v>
       </c>
       <c r="P37" t="n">
-        <v>10.2292649289395</v>
+        <v>10.22926492893949</v>
       </c>
       <c r="Q37" t="n">
         <v>0.9863195419311523</v>
@@ -7816,7 +7816,7 @@
         <v>130.1019627997216</v>
       </c>
       <c r="S37" t="n">
-        <v>16.04033125207781</v>
+        <v>16.0403312520778</v>
       </c>
       <c r="T37" t="n">
         <v>0.9942533373832703</v>
@@ -7834,7 +7834,7 @@
         <v>80.98474867800449</v>
       </c>
       <c r="Y37" t="n">
-        <v>24.99514640645779</v>
+        <v>24.99514640645778</v>
       </c>
       <c r="Z37" t="n">
         <v>0.9931911826133728</v>
@@ -7843,7 +7843,7 @@
         <v>77.63624800012467</v>
       </c>
       <c r="AB37" t="n">
-        <v>16.88696678648606</v>
+        <v>16.88696678648604</v>
       </c>
       <c r="AC37" t="n">
         <v>0.9946804642677307</v>
@@ -7852,7 +7852,7 @@
         <v>81.83665174119017</v>
       </c>
       <c r="AE37" t="n">
-        <v>9.617647211602417</v>
+        <v>9.617647211602394</v>
       </c>
       <c r="AF37" t="n">
         <v>0.9729381799697876</v>
@@ -7861,7 +7861,7 @@
         <v>68.95618844539561</v>
       </c>
       <c r="AH37" t="n">
-        <v>8.360014570520292</v>
+        <v>8.36001457052028</v>
       </c>
       <c r="AI37" t="n">
         <v>0.9984990358352661</v>
@@ -7870,7 +7870,7 @@
         <v>74.37637816084192</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.1890791223404449</v>
+        <v>0.1890791223404255</v>
       </c>
       <c r="AL37" t="n">
         <v>0.9942721128463745</v>
@@ -7897,67 +7897,67 @@
         <v>17.64716493322494</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.204329470370681</v>
+        <v>3.204329470370678</v>
       </c>
       <c r="AU37" t="n">
         <v>0.402049720287323</v>
       </c>
       <c r="AV37" t="n">
-        <v>62.0183086390921</v>
+        <v>-0.1752609902239897</v>
       </c>
       <c r="AW37" t="n">
-        <v>65.55616327378678</v>
+        <v>0.0487388448512327</v>
       </c>
       <c r="AX37" t="n">
+        <v>0.193052088960691</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0.2269988364361737</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0.3657401876246666</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>-0.1274595869348403</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0.6147344061668889</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0.3097148651772379</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0.4551623729949341</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0.3707013231642691</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>62.01830863909207</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>65.55616327378675</v>
+      </c>
+      <c r="BH37" t="n">
         <v>127.5399963175865</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>-0.1752609902239897</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>0.0487388448512327</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>0.193052088960691</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>0.2269988364361737</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>0.3657401876246666</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>-0.1274595869348403</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>0.6147344061668889</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>0.3097148651772379</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>0.4551623729949341</v>
-      </c>
-      <c r="BH37" t="n">
-        <v>0.3707013231642691</v>
       </c>
       <c r="BI37" t="n">
         <v>0.6205030395592672</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0.6006226901338234</v>
+        <v>0.6006226901338341</v>
       </c>
       <c r="BK37" t="n">
-        <v>-0.7771561212346185</v>
+        <v>-0.7771561212346398</v>
       </c>
       <c r="BL37" t="n">
-        <v>3.343439304039013</v>
+        <v>3.343439304039038</v>
       </c>
       <c r="BM37" t="n">
-        <v>2.106298483389608</v>
+        <v>2.106298483389594</v>
       </c>
       <c r="BN37" t="n">
-        <v>3.125707763345652</v>
+        <v>3.125707763345623</v>
       </c>
     </row>
     <row r="38">
@@ -7971,7 +7971,7 @@
         <v>157.8396249324718</v>
       </c>
       <c r="D38" t="n">
-        <v>5.579571013754986</v>
+        <v>5.579571013754987</v>
       </c>
       <c r="E38" t="n">
         <v>0.9996491670608521</v>
@@ -7980,7 +7980,7 @@
         <v>141.436361759267</v>
       </c>
       <c r="G38" t="n">
-        <v>15.56016637923869</v>
+        <v>15.5601663792387</v>
       </c>
       <c r="H38" t="n">
         <v>0.9999518394470215</v>
@@ -7989,7 +7989,7 @@
         <v>136.1355314863489</v>
       </c>
       <c r="J38" t="n">
-        <v>1.689196647481708</v>
+        <v>1.689196647481715</v>
       </c>
       <c r="K38" t="n">
         <v>0.9992794394493103</v>
@@ -7998,7 +7998,7 @@
         <v>131.3579153507314</v>
       </c>
       <c r="M38" t="n">
-        <v>3.818171075049861</v>
+        <v>3.818171075049867</v>
       </c>
       <c r="N38" t="n">
         <v>0.999037504196167</v>
@@ -8007,7 +8007,7 @@
         <v>122.5087023795919</v>
       </c>
       <c r="P38" t="n">
-        <v>10.3398911496426</v>
+        <v>10.33989114964262</v>
       </c>
       <c r="Q38" t="n">
         <v>0.984257698059082</v>
@@ -8016,7 +8016,7 @@
         <v>130.2354285057555</v>
       </c>
       <c r="S38" t="n">
-        <v>15.74758976063828</v>
+        <v>15.7475897606383</v>
       </c>
       <c r="T38" t="n">
         <v>0.994414210319519</v>
@@ -8025,7 +8025,7 @@
         <v>126.7037087298454</v>
       </c>
       <c r="V38" t="n">
-        <v>24.31559461228389</v>
+        <v>24.31559461228391</v>
       </c>
       <c r="W38" t="n">
         <v>0.9917260408401489</v>
@@ -8034,7 +8034,7 @@
         <v>81.79953554843335</v>
       </c>
       <c r="Y38" t="n">
-        <v>25.39145287047043</v>
+        <v>25.39145287047041</v>
       </c>
       <c r="Z38" t="n">
         <v>0.9922822117805481</v>
@@ -8043,7 +8043,7 @@
         <v>78.60626058375583</v>
       </c>
       <c r="AB38" t="n">
-        <v>17.71853832488364</v>
+        <v>17.71853832488365</v>
       </c>
       <c r="AC38" t="n">
         <v>0.9927927255630493</v>
@@ -8052,7 +8052,7 @@
         <v>81.92285578301613</v>
       </c>
       <c r="AE38" t="n">
-        <v>9.760349354845431</v>
+        <v>9.760349354845413</v>
       </c>
       <c r="AF38" t="n">
         <v>0.9606408476829529</v>
@@ -8061,7 +8061,7 @@
         <v>69.14965852778009</v>
       </c>
       <c r="AH38" t="n">
-        <v>9.149754301030583</v>
+        <v>9.149754301030585</v>
       </c>
       <c r="AI38" t="n">
         <v>0.9991849064826965</v>
@@ -8070,7 +8070,7 @@
         <v>74.1532102544257</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.7062546750332501</v>
+        <v>0.7062546750332447</v>
       </c>
       <c r="AL38" t="n">
         <v>0.9970007538795471</v>
@@ -8088,7 +8088,7 @@
         <v>39.03338249693526</v>
       </c>
       <c r="AQ38" t="n">
-        <v>15.14938029837103</v>
+        <v>15.14938029837101</v>
       </c>
       <c r="AR38" t="n">
         <v>0.8171294927597046</v>
@@ -8097,67 +8097,67 @@
         <v>20.9355983328312</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.865213597074472</v>
+        <v>3.865213597074468</v>
       </c>
       <c r="AU38" t="n">
         <v>0.4327878654003143</v>
       </c>
       <c r="AV38" t="n">
-        <v>62.08616753672923</v>
+        <v>-0.1783533299222881</v>
       </c>
       <c r="AW38" t="n">
+        <v>0.06423300885139938</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0.5508219942133508</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0.2723754720484948</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0.2388933871654757</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0.0294117217368246</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.066451377057014</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0.09836846209586625</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.179829049617688</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0.4068922489247377</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>62.08616753672916</v>
+      </c>
+      <c r="BG38" t="n">
         <v>70.11276185758688</v>
       </c>
-      <c r="AX38" t="n">
+      <c r="BH38" t="n">
         <v>134.7800884915475</v>
       </c>
-      <c r="AY38" t="n">
-        <v>-0.1783533299222881</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0.06423300885139938</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0.5508219942133508</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>0.2723754720484948</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>0.2388933871654757</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0.0294117217368246</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.066451377057014</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0.09836846209586625</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>1.179829049617688</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>0.4068922489247377</v>
-      </c>
       <c r="BI38" t="n">
-        <v>2.127933845054599</v>
+        <v>2.127933845054606</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0.9199105080510446</v>
+        <v>0.9199105080510463</v>
       </c>
       <c r="BK38" t="n">
-        <v>3.779725115902615</v>
+        <v>3.779725115902643</v>
       </c>
       <c r="BL38" t="n">
-        <v>0.2059813715983267</v>
+        <v>0.2059813715983196</v>
       </c>
       <c r="BM38" t="n">
-        <v>5.114542668193423</v>
+        <v>5.114542668193408</v>
       </c>
       <c r="BN38" t="n">
-        <v>-1.233754100043456</v>
+        <v>-1.233754100043441</v>
       </c>
     </row>
     <row r="39">
@@ -8171,7 +8171,7 @@
         <v>159.0474230177859</v>
       </c>
       <c r="D39" t="n">
-        <v>5.089065876412889</v>
+        <v>5.089065876412899</v>
       </c>
       <c r="E39" t="n">
         <v>0.9997445940971375</v>
@@ -8180,7 +8180,7 @@
         <v>142.511489543509</v>
       </c>
       <c r="G39" t="n">
-        <v>14.65402156748669</v>
+        <v>14.6540215674867</v>
       </c>
       <c r="H39" t="n">
         <v>0.9998051524162292</v>
@@ -8189,7 +8189,7 @@
         <v>135.8932170462101</v>
       </c>
       <c r="J39" t="n">
-        <v>1.431306879571139</v>
+        <v>1.431306879571144</v>
       </c>
       <c r="K39" t="n">
         <v>0.999442994594574</v>
@@ -8198,7 +8198,7 @@
         <v>131.679867683573</v>
       </c>
       <c r="M39" t="n">
-        <v>3.883670238738347</v>
+        <v>3.883670238738365</v>
       </c>
       <c r="N39" t="n">
         <v>0.9994041919708252</v>
@@ -8207,7 +8207,7 @@
         <v>123.0555676399393</v>
       </c>
       <c r="P39" t="n">
-        <v>9.961392017121</v>
+        <v>9.96139201712101</v>
       </c>
       <c r="Q39" t="n">
         <v>0.9810127019882202</v>
@@ -8216,7 +8216,7 @@
         <v>130.7597383539728</v>
       </c>
       <c r="S39" t="n">
-        <v>15.33128454330119</v>
+        <v>15.3312845433012</v>
       </c>
       <c r="T39" t="n">
         <v>0.9946574568748474</v>
@@ -8225,7 +8225,7 @@
         <v>127.4881971643326</v>
       </c>
       <c r="V39" t="n">
-        <v>23.89073473341921</v>
+        <v>23.89073473341922</v>
       </c>
       <c r="W39" t="n">
         <v>0.9892247319221497</v>
@@ -8243,7 +8243,7 @@
         <v>79.76915075423869</v>
       </c>
       <c r="AB39" t="n">
-        <v>17.97089272357047</v>
+        <v>17.97089272357048</v>
       </c>
       <c r="AC39" t="n">
         <v>0.9867681860923767</v>
@@ -8252,7 +8252,7 @@
         <v>82.31443851552112</v>
       </c>
       <c r="AE39" t="n">
-        <v>9.859823673329458</v>
+        <v>9.859823673329455</v>
       </c>
       <c r="AF39" t="n">
         <v>0.9702966809272766</v>
@@ -8261,7 +8261,7 @@
         <v>70.05783243382231</v>
       </c>
       <c r="AH39" t="n">
-        <v>9.744798376205125</v>
+        <v>9.74479837620512</v>
       </c>
       <c r="AI39" t="n">
         <v>0.9993143081665039</v>
@@ -8270,7 +8270,7 @@
         <v>74.01967150099735</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.9553787556100417</v>
+        <v>0.9553787556100399</v>
       </c>
       <c r="AL39" t="n">
         <v>0.9984355568885803</v>
@@ -8279,7 +8279,7 @@
         <v>68.15455010596743</v>
       </c>
       <c r="AN39" t="n">
-        <v>18.47641315866025</v>
+        <v>18.47641315866024</v>
       </c>
       <c r="AO39" t="n">
         <v>0.9998520612716675</v>
@@ -8297,67 +8297,67 @@
         <v>24.08875810339096</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.501145383144944</v>
+        <v>3.501145383144947</v>
       </c>
       <c r="AU39" t="n">
         <v>0.1759843528270721</v>
       </c>
       <c r="AV39" t="n">
-        <v>66.2741763292013</v>
+        <v>-0.04679497252119091</v>
       </c>
       <c r="AW39" t="n">
-        <v>73.11561350559201</v>
+        <v>0.07958310715695305</v>
       </c>
       <c r="AX39" t="n">
+        <v>0.7378030330576806</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0.03240057762632631</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0.4245636310983159</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0.1523220792729809</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0.8114713303586214</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>-0.3219117509557812</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.26894687084441</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>-0.08681277011303479</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>66.27417632920128</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>73.11561350559204</v>
+      </c>
+      <c r="BH39" t="n">
         <v>137.7690816539734</v>
       </c>
-      <c r="AY39" t="n">
-        <v>-0.04679497252119091</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0.07958310715695305</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0.7378030330576806</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0.03240057762632631</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>0.4245636310983159</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0.1523220792729809</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0.8114713303586214</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>-0.3219117509557812</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>1.26894687084441</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>-0.08681277011303479</v>
-      </c>
       <c r="BI39" t="n">
-        <v>2.460324055661356</v>
+        <v>2.46032405566136</v>
       </c>
       <c r="BJ39" t="n">
-        <v>-0.6107795680626431</v>
+        <v>-0.6107795680626644</v>
       </c>
       <c r="BK39" t="n">
-        <v>-0.365193378037965</v>
+        <v>-0.3651933780380006</v>
       </c>
       <c r="BL39" t="n">
-        <v>-3.989786090956279</v>
+        <v>-3.989786090956319</v>
       </c>
       <c r="BM39" t="n">
-        <v>-0.361209716697303</v>
+        <v>-0.3612097166972887</v>
       </c>
       <c r="BN39" t="n">
-        <v>-4.75658329309244</v>
+        <v>-4.756583293092419</v>
       </c>
     </row>
     <row r="40">
@@ -8371,7 +8371,7 @@
         <v>160.4322879872424</v>
       </c>
       <c r="D40" t="n">
-        <v>4.984948990192805</v>
+        <v>4.984948990192819</v>
       </c>
       <c r="E40" t="n">
         <v>0.9987649917602539</v>
@@ -8380,7 +8380,7 @@
         <v>143.7439127171293</v>
       </c>
       <c r="G40" t="n">
-        <v>14.65082371488529</v>
+        <v>14.65082371488531</v>
       </c>
       <c r="H40" t="n">
         <v>0.999738872051239</v>
@@ -8389,7 +8389,7 @@
         <v>136.0923685926072</v>
       </c>
       <c r="J40" t="n">
-        <v>1.795618584815486</v>
+        <v>1.795618584815492</v>
       </c>
       <c r="K40" t="n">
         <v>0.9991142153739929</v>
@@ -8398,7 +8398,7 @@
         <v>131.6150827610746</v>
       </c>
       <c r="M40" t="n">
-        <v>3.881040532538208</v>
+        <v>3.881040532538232</v>
       </c>
       <c r="N40" t="n">
         <v>0.9990624785423279</v>
@@ -8407,7 +8407,7 @@
         <v>123.8317124387051</v>
       </c>
       <c r="P40" t="n">
-        <v>10.58252212849067</v>
+        <v>10.58252212849069</v>
       </c>
       <c r="Q40" t="n">
         <v>0.9882760643959045</v>
@@ -8416,7 +8416,7 @@
         <v>131.9381957358502</v>
       </c>
       <c r="S40" t="n">
-        <v>15.25891892453456</v>
+        <v>15.25891892453457</v>
       </c>
       <c r="T40" t="n">
         <v>0.9921106696128845</v>
@@ -8425,7 +8425,7 @@
         <v>128.5085881010015</v>
       </c>
       <c r="V40" t="n">
-        <v>23.54836971201794</v>
+        <v>23.54836971201795</v>
       </c>
       <c r="W40" t="n">
         <v>0.9906127452850342</v>
@@ -8443,7 +8443,7 @@
         <v>80.22920324447307</v>
       </c>
       <c r="AB40" t="n">
-        <v>17.93419046604888</v>
+        <v>17.93419046604887</v>
       </c>
       <c r="AC40" t="n">
         <v>0.9873629808425903</v>
@@ -8452,7 +8452,7 @@
         <v>82.77198304521276</v>
       </c>
       <c r="AE40" t="n">
-        <v>9.79721393991025</v>
+        <v>9.79721393991024</v>
       </c>
       <c r="AF40" t="n">
         <v>0.9700224995613098</v>
@@ -8461,7 +8461,7 @@
         <v>70.62526459389545</v>
       </c>
       <c r="AH40" t="n">
-        <v>10.48988179957612</v>
+        <v>10.48988179957613</v>
       </c>
       <c r="AI40" t="n">
         <v>0.9992142915725708</v>
@@ -8470,7 +8470,7 @@
         <v>74.05962030938332</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.9135956459857084</v>
+        <v>0.9135956459857049</v>
       </c>
       <c r="AL40" t="n">
         <v>0.9982661604881287</v>
@@ -8479,7 +8479,7 @@
         <v>69.3515696424119</v>
       </c>
       <c r="AN40" t="n">
-        <v>18.81077543218086</v>
+        <v>18.81077543218085</v>
       </c>
       <c r="AO40" t="n">
         <v>0.9999135732650757</v>
@@ -8497,67 +8497,67 @@
         <v>26.38357649458216</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.578234733419208</v>
+        <v>3.578234733419216</v>
       </c>
       <c r="AU40" t="n">
         <v>0.5948168635368347</v>
       </c>
       <c r="AV40" t="n">
-        <v>67.00681564805194</v>
+        <v>-0.01918711560838204</v>
       </c>
       <c r="AW40" t="n">
-        <v>69.38237510151095</v>
+        <v>0.02030108837371003</v>
       </c>
       <c r="AX40" t="n">
+        <v>0.6156231494660034</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>-0.1420041348071805</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0.5435375457114375</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0.112973882796922</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0.4226278751454515</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0.1633887595318768</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.006203509391618</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>-0.008593214319102316</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>67.00681564805188</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>69.38237510151087</v>
+      </c>
+      <c r="BH40" t="n">
         <v>134.0576690581529</v>
       </c>
-      <c r="AY40" t="n">
-        <v>-0.01918711560838204</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0.02030108837371003</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0.6156231494660034</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>-0.1420041348071805</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>0.5435375457114375</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>0.112973882796922</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>0.4226278751454515</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>0.1633887595318768</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>1.006203509391618</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>-0.008593214319102316</v>
-      </c>
       <c r="BI40" t="n">
-        <v>0.906374708929313</v>
+        <v>0.9063747089292775</v>
       </c>
       <c r="BJ40" t="n">
-        <v>-0.842779243140809</v>
+        <v>-0.8427792431407859</v>
       </c>
       <c r="BK40" t="n">
-        <v>-4.199847066009944</v>
+        <v>-4.199847066009994</v>
       </c>
       <c r="BL40" t="n">
-        <v>0.815730181756301</v>
+        <v>0.81573018175634</v>
       </c>
       <c r="BM40" t="n">
-        <v>-4.398623917991458</v>
+        <v>-4.398623917991429</v>
       </c>
       <c r="BN40" t="n">
-        <v>1.419297706146253</v>
+        <v>1.419297706146232</v>
       </c>
     </row>
     <row r="41">
@@ -8571,7 +8571,7 @@
         <v>161.8271361006067</v>
       </c>
       <c r="D41" t="n">
-        <v>5.248439058344417</v>
+        <v>5.248439058344415</v>
       </c>
       <c r="E41" t="n">
         <v>0.999562680721283</v>
@@ -8589,7 +8589,7 @@
         <v>136.1932795098487</v>
       </c>
       <c r="J41" t="n">
-        <v>2.111037234042556</v>
+        <v>2.111037234042553</v>
       </c>
       <c r="K41" t="n">
         <v>0.999142050743103</v>
@@ -8598,7 +8598,7 @@
         <v>132.0240426570811</v>
       </c>
       <c r="M41" t="n">
-        <v>4.244751625872681</v>
+        <v>4.244751625872673</v>
       </c>
       <c r="N41" t="n">
         <v>0.9996168613433838</v>
@@ -8607,7 +8607,7 @@
         <v>124.790362094311</v>
       </c>
       <c r="P41" t="n">
-        <v>11.20047062001331</v>
+        <v>11.2004706200133</v>
       </c>
       <c r="Q41" t="n">
         <v>0.989474356174469</v>
@@ -8643,7 +8643,7 @@
         <v>80.6144065045296</v>
       </c>
       <c r="AB41" t="n">
-        <v>17.96027650224403</v>
+        <v>17.96027650224402</v>
       </c>
       <c r="AC41" t="n">
         <v>0.9965711832046509</v>
@@ -8652,7 +8652,7 @@
         <v>83.40151360694399</v>
       </c>
       <c r="AE41" t="n">
-        <v>9.549388479679209</v>
+        <v>9.549388479679189</v>
       </c>
       <c r="AF41" t="n">
         <v>0.9662514925003052</v>
@@ -8670,7 +8670,7 @@
         <v>73.98129726978058</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.9521809030086388</v>
+        <v>0.9521809030086437</v>
       </c>
       <c r="AL41" t="n">
         <v>0.9991223216056824</v>
@@ -8679,7 +8679,7 @@
         <v>70.29932711986785</v>
       </c>
       <c r="AN41" t="n">
-        <v>19.37772060962433</v>
+        <v>19.37772060962434</v>
       </c>
       <c r="AO41" t="n">
         <v>0.9991262555122375</v>
@@ -8688,7 +8688,7 @@
         <v>43.19053406411029</v>
       </c>
       <c r="AQ41" t="n">
-        <v>15.45815975108047</v>
+        <v>15.45815975108045</v>
       </c>
       <c r="AR41" t="n">
         <v>0.8831926584243774</v>
@@ -8697,67 +8697,67 @@
         <v>28.28060921202315</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.315978354596098</v>
+        <v>3.315978354596077</v>
       </c>
       <c r="AU41" t="n">
         <v>0.3285631537437439</v>
       </c>
       <c r="AV41" t="n">
-        <v>68.08692574705992</v>
+        <v>-0.006192795773770854</v>
       </c>
       <c r="AW41" t="n">
-        <v>64.71591937357212</v>
+        <v>0.04256228183178834</v>
       </c>
       <c r="AX41" t="n">
-        <v>128.9718338179904</v>
+        <v>0.4537947634433195</v>
       </c>
       <c r="AY41" t="n">
-        <v>-0.006192795773770854</v>
+        <v>-0.1859238807191161</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.04256228183178834</v>
+        <v>0.6505113966921598</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.4537947634433195</v>
+        <v>0.06397734297082636</v>
       </c>
       <c r="BB41" t="n">
-        <v>-0.1859238807191161</v>
+        <v>1.138248849422375</v>
       </c>
       <c r="BC41" t="n">
-        <v>0.6505113966921598</v>
+        <v>0.7343332818213852</v>
       </c>
       <c r="BD41" t="n">
-        <v>0.06397734297082636</v>
+        <v>1.251760442206205</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.138248849422375</v>
+        <v>0.2389664345599307</v>
       </c>
       <c r="BF41" t="n">
-        <v>0.7343332818213852</v>
+        <v>68.08692574705984</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.251760442206205</v>
+        <v>64.71591937357205</v>
       </c>
       <c r="BH41" t="n">
-        <v>0.2389664345599307</v>
+        <v>128.9718338179905</v>
       </c>
       <c r="BI41" t="n">
-        <v>0.7747655693797384</v>
+        <v>0.7747655693797881</v>
       </c>
       <c r="BJ41" t="n">
-        <v>-0.218476834588909</v>
+        <v>-0.2184768345888273</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.266266985474637</v>
+        <v>1.26626698547468</v>
       </c>
       <c r="BL41" t="n">
-        <v>5.699418382449021</v>
+        <v>5.699418382449089</v>
       </c>
       <c r="BM41" t="n">
-        <v>2.477385695595203</v>
+        <v>2.477385695595174</v>
       </c>
       <c r="BN41" t="n">
-        <v>7.219615274672144</v>
+        <v>7.219615274672087</v>
       </c>
     </row>
     <row r="42">
@@ -8771,7 +8771,7 @@
         <v>162.8635325330369</v>
       </c>
       <c r="D42" t="n">
-        <v>5.067687338971098</v>
+        <v>5.067687338971077</v>
       </c>
       <c r="E42" t="n">
         <v>0.9996787309646606</v>
@@ -8780,7 +8780,7 @@
         <v>146.2183039239112</v>
       </c>
       <c r="G42" t="n">
-        <v>14.71211859520446</v>
+        <v>14.71211859520445</v>
       </c>
       <c r="H42" t="n">
         <v>0.9997664093971252</v>
@@ -8789,7 +8789,7 @@
         <v>136.1573970064204</v>
       </c>
       <c r="J42" t="n">
-        <v>2.18895445478725</v>
+        <v>2.188954454787234</v>
       </c>
       <c r="K42" t="n">
         <v>0.9991629123687744</v>
@@ -8798,7 +8798,7 @@
         <v>131.9279285187417</v>
       </c>
       <c r="M42" t="n">
-        <v>3.964265863946139</v>
+        <v>3.964265863946144</v>
       </c>
       <c r="N42" t="n">
         <v>0.9996237754821777</v>
@@ -8807,7 +8807,7 @@
         <v>125.7566736099568</v>
       </c>
       <c r="P42" t="n">
-        <v>11.483537389877</v>
+        <v>11.48353738987699</v>
       </c>
       <c r="Q42" t="n">
         <v>0.9866771697998047</v>
@@ -8825,7 +8825,7 @@
         <v>131.233807827564</v>
       </c>
       <c r="V42" t="n">
-        <v>24.24548534636804</v>
+        <v>24.24548534636802</v>
       </c>
       <c r="W42" t="n">
         <v>0.9887056946754456</v>
@@ -8834,7 +8834,7 @@
         <v>86.84095017453458</v>
       </c>
       <c r="Y42" t="n">
-        <v>25.18185554666721</v>
+        <v>25.18185554666722</v>
       </c>
       <c r="Z42" t="n">
         <v>0.9893559813499451</v>
@@ -8843,7 +8843,7 @@
         <v>82.50570094331782</v>
       </c>
       <c r="AB42" t="n">
-        <v>17.86890232816654</v>
+        <v>17.86890232816656</v>
       </c>
       <c r="AC42" t="n">
         <v>0.9955537915229797</v>
@@ -8852,7 +8852,7 @@
         <v>84.07300583859708</v>
       </c>
       <c r="AE42" t="n">
-        <v>9.267912519739014</v>
+        <v>9.26791251973903</v>
       </c>
       <c r="AF42" t="n">
         <v>0.9312916994094849</v>
@@ -8861,7 +8861,7 @@
         <v>71.53285412078209</v>
       </c>
       <c r="AH42" t="n">
-        <v>10.97628005007479</v>
+        <v>10.9762800500748</v>
       </c>
       <c r="AI42" t="n">
         <v>0.9968852400779724</v>
@@ -8870,7 +8870,7 @@
         <v>74.04723471783578</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.6508360517785832</v>
+        <v>0.6508360517785905</v>
       </c>
       <c r="AL42" t="n">
         <v>0.9994354844093323</v>
@@ -8879,7 +8879,7 @@
         <v>71.26709146702544</v>
       </c>
       <c r="AN42" t="n">
-        <v>18.95079917096078</v>
+        <v>18.95079917096077</v>
       </c>
       <c r="AO42" t="n">
         <v>0.999708354473114</v>
@@ -8897,67 +8897,67 @@
         <v>30.62710660569211</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.015331511801861</v>
+        <v>3.015331511801862</v>
       </c>
       <c r="AU42" t="n">
         <v>0.217385545372963</v>
       </c>
       <c r="AV42" t="n">
-        <v>68.55634678681142</v>
+        <v>0.06593744805519464</v>
       </c>
       <c r="AW42" t="n">
-        <v>71.91490907246022</v>
+        <v>0.07213024382896549</v>
       </c>
       <c r="AX42" t="n">
-        <v>139.0124404493433</v>
+        <v>0.2437753880277711</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.06593744805519464</v>
+        <v>-0.2100193754155484</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.07213024382896549</v>
+        <v>0.6714922316530902</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.2437753880277711</v>
+        <v>0.02098083496093039</v>
       </c>
       <c r="BB42" t="n">
-        <v>-0.2100193754155484</v>
+        <v>1.891294438788222</v>
       </c>
       <c r="BC42" t="n">
-        <v>0.6714922316530902</v>
+        <v>0.753045589365847</v>
       </c>
       <c r="BD42" t="n">
-        <v>0.02098083496093039</v>
+        <v>1.484136378511479</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.891294438788222</v>
+        <v>0.2323759363052744</v>
       </c>
       <c r="BF42" t="n">
-        <v>0.753045589365847</v>
+        <v>68.55634678681146</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.484136378511479</v>
+        <v>71.91490907246023</v>
       </c>
       <c r="BH42" t="n">
-        <v>0.2323759363052744</v>
+        <v>139.0124404493432</v>
       </c>
       <c r="BI42" t="n">
-        <v>0.4694210397514951</v>
+        <v>0.469421039751623</v>
       </c>
       <c r="BJ42" t="n">
-        <v>-0.3053445296282433</v>
+        <v>-0.3053445296281652</v>
       </c>
       <c r="BK42" t="n">
-        <v>7.198989698888099</v>
+        <v>7.198989698888184</v>
       </c>
       <c r="BL42" t="n">
-        <v>5.932722713413462</v>
+        <v>5.932722713413504</v>
       </c>
       <c r="BM42" t="n">
-        <v>10.04060663135283</v>
+        <v>10.04060663135274</v>
       </c>
       <c r="BN42" t="n">
-        <v>7.563220935757627</v>
+        <v>7.56322093575757</v>
       </c>
     </row>
   </sheetData>
